--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T13:19:08+00:00</t>
+    <t>2025-12-23T13:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T13:30:37+00:00</t>
+    <t>2025-12-23T13:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T13:47:13+00:00</t>
+    <t>2025-12-23T14:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T14:00:44+00:00</t>
+    <t>2025-12-23T14:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T14:16:40+00:00</t>
+    <t>2025-12-29T12:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21110" uniqueCount="1638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21110" uniqueCount="1637">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T12:28:59+00:00</t>
+    <t>2025-12-29T12:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Range with low and high unit UCUM or EDQM codes if code is used</t>
+    <t>Range with low and high unit UCUM or EDQM codes if code is used
+Plage avec des unités UCUM ou EDQM si un code est utilisé.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -370,7 +371,8 @@
     <t>Ratio with UCUM or EDQM codes if code is used</t>
   </si>
   <si>
-    <t>Ratio with numerator and denominator unit UCUM or EDQM encoded if code is used</t>
+    <t>Ratio with numerator and denominator unit UCUM or EDQM encoded if code is used
+Ratio avec des unités UCUM ou EDQM si un code est utilisé.</t>
   </si>
   <si>
     <t>Ratio</t>
@@ -425,7 +427,8 @@
     <t>SimpleQuantity with UCUM or EDQM codes or code not used</t>
   </si>
   <si>
-    <t>simple quantity datatype requiring a UCUM or EDQM code or no code (only unti)</t>
+    <t>Simple quantity datatype requiring a UCUM or EDQM code or no code (only unit)
+SimpleQuantity avec des unités UCUM ou EDQM si un code est utilisé.</t>
   </si>
   <si>
     <t>Quantity</t>
@@ -779,7 +782,8 @@
     <t>FR Inpatient MedicationRequest</t>
   </si>
   <si>
-    <t>French inpatient medication request profile</t>
+    <t>French inpatient medication request profile
+Profil français de modélisation de la ligne de prescription médicamenteuse en milieu hospitalier.</t>
   </si>
   <si>
     <t>resource</t>
@@ -2848,7 +2852,8 @@
     <t>FR Medication Compound</t>
   </si>
   <si>
-    <t>A complex medication composed of two to many simple medication. The simple medications component are described in as many ingredient.itemReference referencing a Medication resource profiled fr-medication-non-compound.</t>
+    <t>A complex medication composed of two to many simple medication. The simple medications component are described in as many ingredient.itemReference referencing a Medication resource profiled fr-medication-non-compound.
+Profil de la ressource Medication décrivant un médicament composé de deux à plusieurs médicaments simples. Les composants médicaments simples sont décrits dans autant d'éléments ingredient.itemReference référencant une ressource Medication profilée fr-medication-non-compound.</t>
   </si>
   <si>
     <t>Compound medication description</t>
@@ -3104,7 +3109,8 @@
     <t>FR Medication Non Compound</t>
   </si>
   <si>
-    <t>Simple prescribed, dispensed, administered or used medication composed of one to many substances. If composed of many substance, the strengh SHALL be defined.</t>
+    <t>Simple prescribed, dispensed, administered or used medication composed of one to many substances. If composed of many substance, the strengh SHALL be defined. This ressource is profiled for describing a simple medication (vs compound medication) in the presription line represented by a MedicationRequest, a MedicationDispense or a MedicationUsage (pka MedicationStatement).
+Profil de la ressource Medication décrivant un médicament simple (vs médicament composé) dans la ligne de prescription, la dispensation ou l'administration représentée par une MedicationRequest, une MedicationDispense ou une MedicationStatement. Si le médicament est composé de plusieurs substances, la concentration de chaque substance doit être définie (ingredient.strength).</t>
   </si>
   <si>
     <t>Simple medication description, include those composed of many substances.</t>
@@ -3113,7 +3119,7 @@
     <t>Simple Medication</t>
   </si>
   <si>
-    <t>This ressource is profiled for describing a simple medication (vs compound medication) in the presription line represented by a MedicationRequest, a MedicationDispense or a MedicationUsage (pka MedicationStatement).</t>
+    <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
   </si>
   <si>
     <t>A simple medication is made of one single component made of one to many substances.
@@ -3239,16 +3245,14 @@
     <t>FR Medication</t>
   </si>
   <si>
-    <t>profil de la ressource Medication décrivant le médicament dans une ressource MedicationRequest ou MedicationStatement profilée par InterOp'Santé</t>
-  </si>
-  <si>
-    <t>décrit le médicament figurant dans une ressource InterOp'Santé (fr) MedicationStatement (Bilan Médicamenteux, Conciliation) ou MedicationRequest (prescription)</t>
+    <t>French medication profile
+Profil de la ressource Medication décrivant le médicament. Ce profil peut être référencé dans une ressource MedicationRequest ou MedicationStatement profilée par Interop'Santé afin de décrire le médicament prescrit ou le médicament déclaré dans un bilan médicamenteux ou une conciliation médicamenteuse.</t>
+  </si>
+  <si>
+    <t>décrit le médicament figurant dans une ressource Interop'Santé (fr) MedicationStatement (Bilan Médicamenteux, Conciliation) ou MedicationRequest (prescription)</t>
   </si>
   <si>
     <t>Definition of a Medication</t>
-  </si>
-  <si>
-    <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
   </si>
   <si>
     <t>A coded concept defining the form of a medication.</t>
@@ -3322,7 +3326,8 @@
     <t>FR Medication Request</t>
   </si>
   <si>
-    <t>French medication request profile</t>
+    <t>French medication request profile
+Profil français de modélisation de la ligne de prescription médicamenteuse.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/StructureDefinition/MedicationRequest</t>
@@ -3340,7 +3345,8 @@
     <t>FR Medicinal Product Substance</t>
   </si>
   <si>
-    <t>code for the medicinal product substance</t>
+    <t>A FHIR CodeableConcept profile representing a coded medicinal product substance 
+Profil FHIR CodeableConcept représentant une substance de produit médicamenteux codée selon le référentiel des substances médicamenteuses RIUM (Répertoire International des Substances Médicamenteuses de l'ANS).</t>
   </si>
   <si>
     <t>CodeableConcept</t>
@@ -3392,7 +3398,8 @@
     <t>FR Observation For Prescription</t>
   </si>
   <si>
-    <t>Observation provided as context of the prescription (ex. weight, height...)</t>
+    <t>French observation profile for prescription purposes. Observation provided as context of the prescription (ex. weight, height...)
+Profil français de modélisation de la ressource Observation pour les besoins de la prescription. Observation fournissant un contexte à la prescription (ex. poids, taille...).</t>
   </si>
   <si>
     <t>Observation</t>
@@ -4493,7 +4500,8 @@
     <t>FR RequestGroup For Prescription</t>
   </si>
   <si>
-    <t>RequestGroup for expressing links between lines of a prescription</t>
+    <t>RequestGroup for expressing links between lines of a prescription
+Profil de la ressource RequestGroup pour exprimer les liens entre les lignes d'une prescription.</t>
   </si>
   <si>
     <t>RequestGroup</t>
@@ -7530,7 +7538,7 @@
         <v>2</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="294">
@@ -7538,7 +7546,7 @@
         <v>4</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="295">
@@ -7554,7 +7562,7 @@
         <v>8</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="297">
@@ -7562,7 +7570,7 @@
         <v>9</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="298">
@@ -7624,7 +7632,7 @@
         <v>23</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="306">
@@ -7692,7 +7700,7 @@
         <v>179</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="315">
@@ -7708,7 +7716,7 @@
         <v>2</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="317">
@@ -7732,7 +7740,7 @@
         <v>8</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="320">
@@ -7740,7 +7748,7 @@
         <v>9</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="321">
@@ -7802,7 +7810,7 @@
         <v>23</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="329">
@@ -7846,7 +7854,7 @@
         <v>33</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="335">
@@ -7878,7 +7886,7 @@
         <v>2</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="339">
@@ -7886,7 +7894,7 @@
         <v>4</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="340">
@@ -7902,7 +7910,7 @@
         <v>8</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="342">
@@ -7910,7 +7918,7 @@
         <v>9</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="343">
@@ -7974,7 +7982,7 @@
         <v>23</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="351">
@@ -8010,7 +8018,7 @@
         <v>31</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="356">
@@ -8018,7 +8026,7 @@
         <v>33</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="357">
@@ -8050,7 +8058,7 @@
         <v>2</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="361">
@@ -8058,7 +8066,7 @@
         <v>4</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="362">
@@ -8074,7 +8082,7 @@
         <v>8</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="364">
@@ -8082,7 +8090,7 @@
         <v>9</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="365">
@@ -8144,7 +8152,7 @@
         <v>23</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="373">
@@ -8180,7 +8188,7 @@
         <v>31</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="378">
@@ -8188,7 +8196,7 @@
         <v>33</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="379">
@@ -8220,7 +8228,7 @@
         <v>2</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="383">
@@ -8228,7 +8236,7 @@
         <v>4</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="384">
@@ -8244,7 +8252,7 @@
         <v>8</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="386">
@@ -8252,7 +8260,7 @@
         <v>9</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="387">
@@ -8314,7 +8322,7 @@
         <v>23</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="395">
@@ -8322,7 +8330,7 @@
         <v>25</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="396">
@@ -8352,7 +8360,7 @@
         <v>31</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="400">
@@ -8360,7 +8368,7 @@
         <v>33</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="401">
@@ -8392,7 +8400,7 @@
         <v>2</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="405">
@@ -8400,7 +8408,7 @@
         <v>4</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="406">
@@ -8416,7 +8424,7 @@
         <v>8</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="408">
@@ -8424,7 +8432,7 @@
         <v>9</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="409">
@@ -8488,7 +8496,7 @@
         <v>23</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="417">
@@ -8524,7 +8532,7 @@
         <v>31</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="422">
@@ -8532,7 +8540,7 @@
         <v>33</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="423">
@@ -8564,7 +8572,7 @@
         <v>2</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="427">
@@ -8588,7 +8596,7 @@
         <v>8</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="430">
@@ -8596,7 +8604,7 @@
         <v>9</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="431">
@@ -8658,7 +8666,7 @@
         <v>23</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="439">
@@ -8726,7 +8734,7 @@
         <v>179</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>1632</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="448">
@@ -8742,7 +8750,7 @@
         <v>2</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>1633</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="450">
@@ -8750,7 +8758,7 @@
         <v>4</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="451">
@@ -8766,7 +8774,7 @@
         <v>8</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="453">
@@ -8904,7 +8912,7 @@
         <v>179</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1636</v>
+        <v>1635</v>
       </c>
     </row>
   </sheetData>
@@ -38354,7 +38362,7 @@
         <v>1040</v>
       </c>
       <c r="N282" t="s" s="2">
-        <v>1041</v>
+        <v>999</v>
       </c>
       <c r="O282" s="2"/>
       <c r="P282" s="2"/>
@@ -39747,10 +39755,10 @@
         <v>232</v>
       </c>
       <c r="Z295" t="s" s="2">
+        <v>1041</v>
+      </c>
+      <c r="AA295" t="s" s="2">
         <v>1042</v>
-      </c>
-      <c r="AA295" t="s" s="2">
-        <v>1043</v>
       </c>
       <c r="AB295" t="s" s="2">
         <v>75</v>
@@ -39824,7 +39832,7 @@
       </c>
       <c r="O296" s="2"/>
       <c r="P296" t="s" s="2">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="Q296" t="s" s="2">
         <v>75</v>
@@ -39925,7 +39933,7 @@
         <v>1022</v>
       </c>
       <c r="N297" t="s" s="2">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="O297" t="s" s="2">
         <v>1024</v>
@@ -40323,7 +40331,7 @@
         <v>75</v>
       </c>
       <c r="F301" t="s" s="2">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="G301" t="s" s="2">
         <v>85</v>
@@ -40347,11 +40355,11 @@
         <v>971</v>
       </c>
       <c r="N301" t="s" s="2">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="O301" s="2"/>
       <c r="P301" t="s" s="2">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="Q301" t="s" s="2">
         <v>75</v>
@@ -40554,16 +40562,16 @@
         <v>743</v>
       </c>
       <c r="M303" t="s" s="2">
+        <v>1048</v>
+      </c>
+      <c r="N303" t="s" s="2">
         <v>1049</v>
       </c>
-      <c r="N303" t="s" s="2">
+      <c r="O303" t="s" s="2">
         <v>1050</v>
       </c>
-      <c r="O303" t="s" s="2">
+      <c r="P303" t="s" s="2">
         <v>1051</v>
-      </c>
-      <c r="P303" t="s" s="2">
-        <v>1052</v>
       </c>
       <c r="Q303" t="s" s="2">
         <v>75</v>
@@ -41253,7 +41261,7 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>177</v>
@@ -41285,10 +41293,10 @@
         <v>78</v>
       </c>
       <c r="M310" t="s" s="2">
+        <v>1055</v>
+      </c>
+      <c r="N310" t="s" s="2">
         <v>1056</v>
-      </c>
-      <c r="N310" t="s" s="2">
-        <v>1057</v>
       </c>
       <c r="O310" s="2"/>
       <c r="P310" s="2"/>
@@ -41356,7 +41364,7 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>182</v>
@@ -41459,7 +41467,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>183</v>
@@ -41562,7 +41570,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>185</v>
@@ -41608,7 +41616,7 @@
       </c>
       <c r="R313" s="2"/>
       <c r="S313" t="s" s="2">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="T313" t="s" s="2">
         <v>75</v>
@@ -41667,7 +41675,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>189</v>
@@ -41733,7 +41741,7 @@
       </c>
       <c r="Z314" s="2"/>
       <c r="AA314" t="s" s="2">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AB314" t="s" s="2">
         <v>75</v>
@@ -41768,7 +41776,7 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>250</v>
@@ -41871,7 +41879,7 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>256</v>
@@ -41976,7 +41984,7 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>262</v>
@@ -42079,7 +42087,7 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>267</v>
@@ -42184,7 +42192,7 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B319" t="s" s="2">
         <v>272</v>
@@ -42289,7 +42297,7 @@
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B320" t="s" s="2">
         <v>280</v>
@@ -42394,7 +42402,7 @@
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B321" t="s" s="2">
         <v>287</v>
@@ -42499,7 +42507,7 @@
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B322" t="s" s="2">
         <v>294</v>
@@ -42600,7 +42608,7 @@
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>296</v>
@@ -42705,7 +42713,7 @@
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B324" t="s" s="2">
         <v>301</v>
@@ -42810,7 +42818,7 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B325" t="s" s="2">
         <v>306</v>
@@ -42913,7 +42921,7 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B326" t="s" s="2">
         <v>308</v>
@@ -43016,7 +43024,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B327" t="s" s="2">
         <v>310</v>
@@ -43121,7 +43129,7 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B328" t="s" s="2">
         <v>313</v>
@@ -43226,7 +43234,7 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B329" t="s" s="2">
         <v>321</v>
@@ -43329,7 +43337,7 @@
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B330" t="s" s="2">
         <v>323</v>
@@ -43434,7 +43442,7 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B331" t="s" s="2">
         <v>325</v>
@@ -43541,7 +43549,7 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B332" t="s" s="2">
         <v>333</v>
@@ -43648,7 +43656,7 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B333" t="s" s="2">
         <v>340</v>
@@ -43755,7 +43763,7 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B334" t="s" s="2">
         <v>345</v>
@@ -43860,7 +43868,7 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B335" t="s" s="2">
         <v>350</v>
@@ -43965,7 +43973,7 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B336" t="s" s="2">
         <v>356</v>
@@ -44070,7 +44078,7 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B337" t="s" s="2">
         <v>362</v>
@@ -44175,7 +44183,7 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B338" t="s" s="2">
         <v>368</v>
@@ -44280,7 +44288,7 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B339" t="s" s="2">
         <v>374</v>
@@ -44383,7 +44391,7 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B340" t="s" s="2">
         <v>379</v>
@@ -44488,7 +44496,7 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B341" t="s" s="2">
         <v>384</v>
@@ -44591,7 +44599,7 @@
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>388</v>
@@ -44694,7 +44702,7 @@
     </row>
     <row r="343">
       <c r="A343" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B343" t="s" s="2">
         <v>397</v>
@@ -44801,7 +44809,7 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B344" t="s" s="2">
         <v>400</v>
@@ -44906,7 +44914,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B345" t="s" s="2">
         <v>403</v>
@@ -45011,7 +45019,7 @@
     </row>
     <row r="346">
       <c r="A346" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B346" t="s" s="2">
         <v>408</v>
@@ -45116,7 +45124,7 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B347" t="s" s="2">
         <v>413</v>
@@ -45219,7 +45227,7 @@
     </row>
     <row r="348">
       <c r="A348" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B348" t="s" s="2">
         <v>447</v>
@@ -45322,7 +45330,7 @@
     </row>
     <row r="349">
       <c r="A349" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B349" t="s" s="2">
         <v>451</v>
@@ -45425,7 +45433,7 @@
     </row>
     <row r="350">
       <c r="A350" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B350" t="s" s="2">
         <v>455</v>
@@ -45528,7 +45536,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B351" t="s" s="2">
         <v>459</v>
@@ -45633,7 +45641,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B352" t="s" s="2">
         <v>465</v>
@@ -45736,7 +45744,7 @@
     </row>
     <row r="353">
       <c r="A353" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B353" t="s" s="2">
         <v>469</v>
@@ -45841,7 +45849,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B354" t="s" s="2">
         <v>475</v>
@@ -45946,7 +45954,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B355" t="s" s="2">
         <v>480</v>
@@ -46049,7 +46057,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B356" t="s" s="2">
         <v>484</v>
@@ -46152,7 +46160,7 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B357" t="s" s="2">
         <v>487</v>
@@ -46255,7 +46263,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B358" t="s" s="2">
         <v>491</v>
@@ -46360,7 +46368,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B359" t="s" s="2">
         <v>495</v>
@@ -46465,7 +46473,7 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B360" t="s" s="2">
         <v>501</v>
@@ -46568,7 +46576,7 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B361" t="s" s="2">
         <v>505</v>
@@ -46671,7 +46679,7 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B362" t="s" s="2">
         <v>532</v>
@@ -46776,7 +46784,7 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B363" t="s" s="2">
         <v>537</v>
@@ -46879,7 +46887,7 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B364" t="s" s="2">
         <v>538</v>
@@ -46984,7 +46992,7 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B365" t="s" s="2">
         <v>539</v>
@@ -47091,7 +47099,7 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B366" t="s" s="2">
         <v>544</v>
@@ -47196,7 +47204,7 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B367" t="s" s="2">
         <v>550</v>
@@ -47301,7 +47309,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B368" t="s" s="2">
         <v>555</v>
@@ -47408,7 +47416,7 @@
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B369" t="s" s="2">
         <v>563</v>
@@ -47511,7 +47519,7 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B370" t="s" s="2">
         <v>567</v>
@@ -47618,7 +47626,7 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B371" t="s" s="2">
         <v>574</v>
@@ -47721,7 +47729,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B372" t="s" s="2">
         <v>575</v>
@@ -47826,7 +47834,7 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B373" t="s" s="2">
         <v>576</v>
@@ -47933,7 +47941,7 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B374" t="s" s="2">
         <v>577</v>
@@ -48038,7 +48046,7 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B375" t="s" s="2">
         <v>582</v>
@@ -48143,7 +48151,7 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B376" t="s" s="2">
         <v>589</v>
@@ -48246,7 +48254,7 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B377" t="s" s="2">
         <v>590</v>
@@ -48351,7 +48359,7 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B378" t="s" s="2">
         <v>591</v>
@@ -48456,7 +48464,7 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B379" t="s" s="2">
         <v>594</v>
@@ -48559,7 +48567,7 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B380" t="s" s="2">
         <v>599</v>
@@ -48666,7 +48674,7 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B381" t="s" s="2">
         <v>606</v>
@@ -48769,7 +48777,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B382" t="s" s="2">
         <v>610</v>
@@ -48876,7 +48884,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B383" t="s" s="2">
         <v>616</v>
@@ -48983,7 +48991,7 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B384" t="s" s="2">
         <v>620</v>
@@ -49086,7 +49094,7 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B385" t="s" s="2">
         <v>626</v>
@@ -49191,7 +49199,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B386" t="s" s="2">
         <v>631</v>
@@ -49294,7 +49302,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B387" t="s" s="2">
         <v>635</v>
@@ -49397,7 +49405,7 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B388" t="s" s="2">
         <v>638</v>
@@ -49500,7 +49508,7 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B389" t="s" s="2">
         <v>642</v>
@@ -49603,7 +49611,7 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B390" t="s" s="2">
         <v>645</v>
@@ -49706,7 +49714,7 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B391" t="s" s="2">
         <v>651</v>
@@ -49811,7 +49819,7 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B392" t="s" s="2">
         <v>657</v>
@@ -49918,7 +49926,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B393" t="s" s="2">
         <v>665</v>
@@ -50021,7 +50029,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B394" t="s" s="2">
         <v>670</v>
@@ -50126,7 +50134,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B395" t="s" s="2">
         <v>677</v>
@@ -50231,7 +50239,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B396" t="s" s="2">
         <v>685</v>
@@ -50338,7 +50346,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B397" t="s" s="2">
         <v>693</v>
@@ -50441,7 +50449,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B398" t="s" s="2">
         <v>699</v>
@@ -50546,7 +50554,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B399" t="s" s="2">
         <v>706</v>
@@ -50649,7 +50657,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B400" t="s" s="2">
         <v>710</v>
@@ -50752,7 +50760,7 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B401" t="s" s="2">
         <v>711</v>
@@ -50857,7 +50865,7 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B402" t="s" s="2">
         <v>712</v>
@@ -50962,7 +50970,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B403" t="s" s="2">
         <v>715</v>
@@ -51067,7 +51075,7 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B404" t="s" s="2">
         <v>722</v>
@@ -51172,7 +51180,7 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B405" t="s" s="2">
         <v>729</v>
@@ -51281,7 +51289,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B406" t="s" s="2">
         <v>732</v>
@@ -51390,7 +51398,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B407" t="s" s="2">
         <v>734</v>
@@ -51495,7 +51503,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B408" t="s" s="2">
         <v>741</v>
@@ -51604,7 +51612,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B409" t="s" s="2">
         <v>745</v>
@@ -51713,7 +51721,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B410" t="s" s="2">
         <v>747</v>
@@ -51822,7 +51830,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B411" t="s" s="2">
         <v>749</v>
@@ -51929,7 +51937,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B412" t="s" s="2">
         <v>756</v>
@@ -52032,7 +52040,7 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B413" t="s" s="2">
         <v>757</v>
@@ -52137,7 +52145,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B414" t="s" s="2">
         <v>758</v>
@@ -52240,7 +52248,7 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B415" t="s" s="2">
         <v>759</v>
@@ -52343,7 +52351,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B416" t="s" s="2">
         <v>760</v>
@@ -52450,7 +52458,7 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B417" t="s" s="2">
         <v>766</v>
@@ -52555,7 +52563,7 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B418" t="s" s="2">
         <v>771</v>
@@ -52658,7 +52666,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B419" t="s" s="2">
         <v>775</v>
@@ -52761,7 +52769,7 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B420" t="s" s="2">
         <v>776</v>
@@ -52866,7 +52874,7 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B421" t="s" s="2">
         <v>777</v>
@@ -52973,7 +52981,7 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B422" t="s" s="2">
         <v>778</v>
@@ -53078,7 +53086,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B423" t="s" s="2">
         <v>782</v>
@@ -53181,7 +53189,7 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B424" t="s" s="2">
         <v>783</v>
@@ -53286,7 +53294,7 @@
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B425" t="s" s="2">
         <v>784</v>
@@ -53393,7 +53401,7 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B426" t="s" s="2">
         <v>785</v>
@@ -53496,7 +53504,7 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B427" t="s" s="2">
         <v>789</v>
@@ -53599,7 +53607,7 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B428" t="s" s="2">
         <v>793</v>
@@ -53702,7 +53710,7 @@
     </row>
     <row r="429">
       <c r="A429" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B429" t="s" s="2">
         <v>796</v>
@@ -53809,7 +53817,7 @@
     </row>
     <row r="430">
       <c r="A430" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B430" t="s" s="2">
         <v>816</v>
@@ -53914,7 +53922,7 @@
     </row>
     <row r="431">
       <c r="A431" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B431" t="s" s="2">
         <v>820</v>
@@ -54017,7 +54025,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B432" t="s" s="2">
         <v>823</v>
@@ -54122,7 +54130,7 @@
     </row>
     <row r="433">
       <c r="A433" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B433" t="s" s="2">
         <v>835</v>
@@ -54225,7 +54233,7 @@
     </row>
     <row r="434">
       <c r="A434" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B434" t="s" s="2">
         <v>839</v>
@@ -54328,7 +54336,7 @@
     </row>
     <row r="435">
       <c r="A435" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B435" t="s" s="2">
         <v>842</v>
@@ -54431,7 +54439,7 @@
     </row>
     <row r="436">
       <c r="A436" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B436" t="s" s="2">
         <v>843</v>
@@ -54536,7 +54544,7 @@
     </row>
     <row r="437">
       <c r="A437" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B437" t="s" s="2">
         <v>844</v>
@@ -54643,7 +54651,7 @@
     </row>
     <row r="438">
       <c r="A438" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B438" t="s" s="2">
         <v>845</v>
@@ -54748,7 +54756,7 @@
     </row>
     <row r="439">
       <c r="A439" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B439" t="s" s="2">
         <v>851</v>
@@ -54851,7 +54859,7 @@
     </row>
     <row r="440">
       <c r="A440" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B440" t="s" s="2">
         <v>856</v>
@@ -54954,7 +54962,7 @@
     </row>
     <row r="441">
       <c r="A441" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B441" t="s" s="2">
         <v>860</v>
@@ -55059,7 +55067,7 @@
     </row>
     <row r="442">
       <c r="A442" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B442" t="s" s="2">
         <v>866</v>
@@ -55164,13 +55172,13 @@
     </row>
     <row r="443">
       <c r="A443" t="s" s="2">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="D443" s="2"/>
       <c r="E443" t="s" s="2">
@@ -55196,13 +55204,13 @@
         <v>78</v>
       </c>
       <c r="M443" t="s" s="2">
+        <v>1071</v>
+      </c>
+      <c r="N443" t="s" s="2">
         <v>1072</v>
       </c>
-      <c r="N443" t="s" s="2">
+      <c r="O443" t="s" s="2">
         <v>1073</v>
-      </c>
-      <c r="O443" t="s" s="2">
-        <v>1074</v>
       </c>
       <c r="P443" s="2"/>
       <c r="Q443" t="s" s="2">
@@ -55216,7 +55224,7 @@
         <v>75</v>
       </c>
       <c r="U443" t="s" s="2">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="V443" t="s" s="2">
         <v>75</v>
@@ -55252,7 +55260,7 @@
         <v>75</v>
       </c>
       <c r="AG443" t="s" s="2">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="AH443" t="s" s="2">
         <v>76</v>
@@ -55269,13 +55277,13 @@
     </row>
     <row r="444">
       <c r="A444" t="s" s="2">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="D444" s="2"/>
       <c r="E444" t="s" s="2">
@@ -55372,13 +55380,13 @@
     </row>
     <row r="445">
       <c r="A445" t="s" s="2">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="D445" s="2"/>
       <c r="E445" t="s" s="2">
@@ -55477,7 +55485,7 @@
     </row>
     <row r="446">
       <c r="A446" t="s" s="2">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B446" t="s" s="2">
         <v>332</v>
@@ -55546,10 +55554,10 @@
         <v>154</v>
       </c>
       <c r="Z446" t="s" s="2">
+        <v>1077</v>
+      </c>
+      <c r="AA446" t="s" s="2">
         <v>1078</v>
-      </c>
-      <c r="AA446" t="s" s="2">
-        <v>1079</v>
       </c>
       <c r="AB446" t="s" s="2">
         <v>75</v>
@@ -55584,7 +55592,7 @@
     </row>
     <row r="447">
       <c r="A447" t="s" s="2">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B447" t="s" s="2">
         <v>339</v>
@@ -55691,17 +55699,17 @@
     </row>
     <row r="448">
       <c r="A448" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D448" s="2"/>
       <c r="E448" t="s" s="2">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F448" s="2"/>
       <c r="G448" t="s" s="2">
@@ -55723,13 +55731,13 @@
         <v>78</v>
       </c>
       <c r="M448" t="s" s="2">
+        <v>1087</v>
+      </c>
+      <c r="N448" t="s" s="2">
         <v>1088</v>
       </c>
-      <c r="N448" t="s" s="2">
+      <c r="O448" t="s" s="2">
         <v>1089</v>
-      </c>
-      <c r="O448" t="s" s="2">
-        <v>1090</v>
       </c>
       <c r="P448" s="2"/>
       <c r="Q448" t="s" s="2">
@@ -55779,7 +55787,7 @@
         <v>75</v>
       </c>
       <c r="AG448" t="s" s="2">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="AH448" t="s" s="2">
         <v>76</v>
@@ -55791,18 +55799,18 @@
         <v>75</v>
       </c>
       <c r="AK448" t="s" s="2">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D449" s="2"/>
       <c r="E449" t="s" s="2">
@@ -55901,13 +55909,13 @@
     </row>
     <row r="450">
       <c r="A450" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D450" s="2"/>
       <c r="E450" t="s" s="2">
@@ -56004,13 +56012,13 @@
     </row>
     <row r="451">
       <c r="A451" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D451" s="2"/>
       <c r="E451" t="s" s="2">
@@ -56109,13 +56117,13 @@
     </row>
     <row r="452">
       <c r="A452" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="D452" s="2"/>
       <c r="E452" t="s" s="2">
@@ -56214,13 +56222,13 @@
     </row>
     <row r="453">
       <c r="A453" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="D453" s="2"/>
       <c r="E453" t="s" s="2">
@@ -56319,13 +56327,13 @@
     </row>
     <row r="454">
       <c r="A454" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D454" s="2"/>
       <c r="E454" t="s" s="2">
@@ -56424,13 +56432,13 @@
     </row>
     <row r="455">
       <c r="A455" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D455" s="2"/>
       <c r="E455" t="s" s="2">
@@ -56529,13 +56537,13 @@
     </row>
     <row r="456">
       <c r="A456" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="D456" s="2"/>
       <c r="E456" t="s" s="2">
@@ -56636,13 +56644,13 @@
     </row>
     <row r="457">
       <c r="A457" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D457" s="2"/>
       <c r="E457" t="s" s="2">
@@ -56668,14 +56676,14 @@
         <v>346</v>
       </c>
       <c r="M457" t="s" s="2">
+        <v>1100</v>
+      </c>
+      <c r="N457" t="s" s="2">
         <v>1101</v>
-      </c>
-      <c r="N457" t="s" s="2">
-        <v>1102</v>
       </c>
       <c r="O457" s="2"/>
       <c r="P457" t="s" s="2">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="Q457" t="s" s="2">
         <v>75</v>
@@ -56724,7 +56732,7 @@
         <v>75</v>
       </c>
       <c r="AG457" t="s" s="2">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="AH457" t="s" s="2">
         <v>76</v>
@@ -56741,17 +56749,17 @@
     </row>
     <row r="458">
       <c r="A458" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D458" s="2"/>
       <c r="E458" t="s" s="2">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="F458" s="2"/>
       <c r="G458" t="s" s="2">
@@ -56770,17 +56778,17 @@
         <v>102</v>
       </c>
       <c r="L458" t="s" s="2">
+        <v>1105</v>
+      </c>
+      <c r="M458" t="s" s="2">
         <v>1106</v>
       </c>
-      <c r="M458" t="s" s="2">
+      <c r="N458" t="s" s="2">
         <v>1107</v>
-      </c>
-      <c r="N458" t="s" s="2">
-        <v>1108</v>
       </c>
       <c r="O458" s="2"/>
       <c r="P458" t="s" s="2">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="Q458" t="s" s="2">
         <v>75</v>
@@ -56829,7 +56837,7 @@
         <v>75</v>
       </c>
       <c r="AG458" t="s" s="2">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="AH458" t="s" s="2">
         <v>76</v>
@@ -56846,17 +56854,17 @@
     </row>
     <row r="459">
       <c r="A459" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C459" t="s" s="2">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D459" s="2"/>
       <c r="E459" t="s" s="2">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="F459" s="2"/>
       <c r="G459" t="s" s="2">
@@ -56875,16 +56883,16 @@
         <v>102</v>
       </c>
       <c r="L459" t="s" s="2">
+        <v>1111</v>
+      </c>
+      <c r="M459" t="s" s="2">
         <v>1112</v>
       </c>
-      <c r="M459" t="s" s="2">
+      <c r="N459" t="s" s="2">
         <v>1113</v>
       </c>
-      <c r="N459" t="s" s="2">
+      <c r="O459" t="s" s="2">
         <v>1114</v>
-      </c>
-      <c r="O459" t="s" s="2">
-        <v>1115</v>
       </c>
       <c r="P459" s="2"/>
       <c r="Q459" t="s" s="2">
@@ -56934,7 +56942,7 @@
         <v>75</v>
       </c>
       <c r="AG459" t="s" s="2">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="AH459" t="s" s="2">
         <v>76</v>
@@ -56951,13 +56959,13 @@
     </row>
     <row r="460">
       <c r="A460" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C460" t="s" s="2">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D460" s="2"/>
       <c r="E460" t="s" s="2">
@@ -56983,16 +56991,16 @@
         <v>149</v>
       </c>
       <c r="M460" t="s" s="2">
+        <v>1116</v>
+      </c>
+      <c r="N460" t="s" s="2">
         <v>1117</v>
-      </c>
-      <c r="N460" t="s" s="2">
-        <v>1118</v>
       </c>
       <c r="O460" t="s" s="2">
         <v>353</v>
       </c>
       <c r="P460" t="s" s="2">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="Q460" t="s" s="2">
         <v>75</v>
@@ -57020,11 +57028,11 @@
         <v>154</v>
       </c>
       <c r="Z460" t="s" s="2">
+        <v>1119</v>
+      </c>
+      <c r="AA460" t="s" s="2">
         <v>1120</v>
       </c>
-      <c r="AA460" t="s" s="2">
-        <v>1121</v>
-      </c>
       <c r="AB460" t="s" s="2">
         <v>75</v>
       </c>
@@ -57041,7 +57049,7 @@
         <v>75</v>
       </c>
       <c r="AG460" t="s" s="2">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AH460" t="s" s="2">
         <v>85</v>
@@ -57058,13 +57066,13 @@
     </row>
     <row r="461">
       <c r="A461" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C461" t="s" s="2">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D461" s="2"/>
       <c r="E461" t="s" s="2">
@@ -57090,16 +57098,16 @@
         <v>229</v>
       </c>
       <c r="M461" t="s" s="2">
+        <v>1122</v>
+      </c>
+      <c r="N461" t="s" s="2">
         <v>1123</v>
       </c>
-      <c r="N461" t="s" s="2">
+      <c r="O461" t="s" s="2">
         <v>1124</v>
       </c>
-      <c r="O461" t="s" s="2">
+      <c r="P461" t="s" s="2">
         <v>1125</v>
-      </c>
-      <c r="P461" t="s" s="2">
-        <v>1126</v>
       </c>
       <c r="Q461" t="s" s="2">
         <v>75</v>
@@ -57127,11 +57135,11 @@
         <v>276</v>
       </c>
       <c r="Z461" t="s" s="2">
+        <v>1126</v>
+      </c>
+      <c r="AA461" t="s" s="2">
         <v>1127</v>
       </c>
-      <c r="AA461" t="s" s="2">
-        <v>1128</v>
-      </c>
       <c r="AB461" t="s" s="2">
         <v>75</v>
       </c>
@@ -57148,7 +57156,7 @@
         <v>75</v>
       </c>
       <c r="AG461" t="s" s="2">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="AH461" t="s" s="2">
         <v>76</v>
@@ -57165,17 +57173,17 @@
     </row>
     <row r="462">
       <c r="A462" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="C462" t="s" s="2">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D462" s="2"/>
       <c r="E462" t="s" s="2">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="F462" s="2"/>
       <c r="G462" t="s" s="2">
@@ -57197,16 +57205,16 @@
         <v>229</v>
       </c>
       <c r="M462" t="s" s="2">
+        <v>1130</v>
+      </c>
+      <c r="N462" t="s" s="2">
         <v>1131</v>
       </c>
-      <c r="N462" t="s" s="2">
+      <c r="O462" t="s" s="2">
         <v>1132</v>
       </c>
-      <c r="O462" t="s" s="2">
+      <c r="P462" t="s" s="2">
         <v>1133</v>
-      </c>
-      <c r="P462" t="s" s="2">
-        <v>1134</v>
       </c>
       <c r="Q462" t="s" s="2">
         <v>75</v>
@@ -57234,11 +57242,11 @@
         <v>232</v>
       </c>
       <c r="Z462" t="s" s="2">
+        <v>1134</v>
+      </c>
+      <c r="AA462" t="s" s="2">
         <v>1135</v>
       </c>
-      <c r="AA462" t="s" s="2">
-        <v>1136</v>
-      </c>
       <c r="AB462" t="s" s="2">
         <v>75</v>
       </c>
@@ -57255,7 +57263,7 @@
         <v>75</v>
       </c>
       <c r="AG462" t="s" s="2">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="AH462" t="s" s="2">
         <v>85</v>
@@ -57272,13 +57280,13 @@
     </row>
     <row r="463">
       <c r="A463" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C463" t="s" s="2">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D463" s="2"/>
       <c r="E463" t="s" s="2">
@@ -57304,16 +57312,16 @@
         <v>404</v>
       </c>
       <c r="M463" t="s" s="2">
+        <v>1137</v>
+      </c>
+      <c r="N463" t="s" s="2">
         <v>1138</v>
       </c>
-      <c r="N463" t="s" s="2">
+      <c r="O463" t="s" s="2">
         <v>1139</v>
       </c>
-      <c r="O463" t="s" s="2">
+      <c r="P463" t="s" s="2">
         <v>1140</v>
-      </c>
-      <c r="P463" t="s" s="2">
-        <v>1141</v>
       </c>
       <c r="Q463" t="s" s="2">
         <v>75</v>
@@ -57362,7 +57370,7 @@
         <v>75</v>
       </c>
       <c r="AG463" t="s" s="2">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AH463" t="s" s="2">
         <v>76</v>
@@ -57379,13 +57387,13 @@
     </row>
     <row r="464">
       <c r="A464" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D464" s="2"/>
       <c r="E464" t="s" s="2">
@@ -57411,13 +57419,13 @@
         <v>414</v>
       </c>
       <c r="M464" t="s" s="2">
+        <v>1142</v>
+      </c>
+      <c r="N464" t="s" s="2">
         <v>1143</v>
       </c>
-      <c r="N464" t="s" s="2">
+      <c r="O464" t="s" s="2">
         <v>1144</v>
-      </c>
-      <c r="O464" t="s" s="2">
-        <v>1145</v>
       </c>
       <c r="P464" s="2"/>
       <c r="Q464" t="s" s="2">
@@ -57467,7 +57475,7 @@
         <v>75</v>
       </c>
       <c r="AG464" t="s" s="2">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="AH464" t="s" s="2">
         <v>76</v>
@@ -57484,17 +57492,17 @@
     </row>
     <row r="465">
       <c r="A465" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D465" s="2"/>
       <c r="E465" t="s" s="2">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="F465" s="2"/>
       <c r="G465" t="s" s="2">
@@ -57513,19 +57521,19 @@
         <v>102</v>
       </c>
       <c r="L465" t="s" s="2">
+        <v>1147</v>
+      </c>
+      <c r="M465" t="s" s="2">
         <v>1148</v>
       </c>
-      <c r="M465" t="s" s="2">
+      <c r="N465" t="s" s="2">
         <v>1149</v>
       </c>
-      <c r="N465" t="s" s="2">
+      <c r="O465" t="s" s="2">
         <v>1150</v>
       </c>
-      <c r="O465" t="s" s="2">
+      <c r="P465" t="s" s="2">
         <v>1151</v>
-      </c>
-      <c r="P465" t="s" s="2">
-        <v>1152</v>
       </c>
       <c r="Q465" t="s" s="2">
         <v>75</v>
@@ -57574,7 +57582,7 @@
         <v>75</v>
       </c>
       <c r="AG465" t="s" s="2">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="AH465" t="s" s="2">
         <v>76</v>
@@ -57591,17 +57599,17 @@
     </row>
     <row r="466">
       <c r="A466" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D466" s="2"/>
       <c r="E466" t="s" s="2">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="F466" s="2"/>
       <c r="G466" t="s" s="2">
@@ -57620,19 +57628,19 @@
         <v>102</v>
       </c>
       <c r="L466" t="s" s="2">
+        <v>1154</v>
+      </c>
+      <c r="M466" t="s" s="2">
         <v>1155</v>
       </c>
-      <c r="M466" t="s" s="2">
+      <c r="N466" t="s" s="2">
         <v>1156</v>
       </c>
-      <c r="N466" t="s" s="2">
+      <c r="O466" t="s" s="2">
         <v>1157</v>
       </c>
-      <c r="O466" t="s" s="2">
+      <c r="P466" t="s" s="2">
         <v>1158</v>
-      </c>
-      <c r="P466" t="s" s="2">
-        <v>1159</v>
       </c>
       <c r="Q466" t="s" s="2">
         <v>75</v>
@@ -57681,7 +57689,7 @@
         <v>75</v>
       </c>
       <c r="AG466" t="s" s="2">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="AH466" t="s" s="2">
         <v>76</v>
@@ -57698,13 +57706,13 @@
     </row>
     <row r="467">
       <c r="A467" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="D467" s="2"/>
       <c r="E467" t="s" s="2">
@@ -57727,16 +57735,16 @@
         <v>102</v>
       </c>
       <c r="L467" t="s" s="2">
+        <v>1160</v>
+      </c>
+      <c r="M467" t="s" s="2">
         <v>1161</v>
       </c>
-      <c r="M467" t="s" s="2">
+      <c r="N467" t="s" s="2">
         <v>1162</v>
       </c>
-      <c r="N467" t="s" s="2">
+      <c r="O467" t="s" s="2">
         <v>1163</v>
-      </c>
-      <c r="O467" t="s" s="2">
-        <v>1164</v>
       </c>
       <c r="P467" s="2"/>
       <c r="Q467" t="s" s="2">
@@ -57786,7 +57794,7 @@
         <v>75</v>
       </c>
       <c r="AG467" t="s" s="2">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="AH467" t="s" s="2">
         <v>76</v>
@@ -57803,13 +57811,13 @@
     </row>
     <row r="468">
       <c r="A468" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D468" s="2"/>
       <c r="E468" t="s" s="2">
@@ -57832,17 +57840,17 @@
         <v>102</v>
       </c>
       <c r="L468" t="s" s="2">
+        <v>1165</v>
+      </c>
+      <c r="M468" t="s" s="2">
         <v>1166</v>
       </c>
-      <c r="M468" t="s" s="2">
+      <c r="N468" t="s" s="2">
         <v>1167</v>
-      </c>
-      <c r="N468" t="s" s="2">
-        <v>1168</v>
       </c>
       <c r="O468" s="2"/>
       <c r="P468" t="s" s="2">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="Q468" t="s" s="2">
         <v>75</v>
@@ -57891,7 +57899,7 @@
         <v>75</v>
       </c>
       <c r="AG468" t="s" s="2">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="AH468" t="s" s="2">
         <v>76</v>
@@ -57908,13 +57916,13 @@
     </row>
     <row r="469">
       <c r="A469" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="D469" s="2"/>
       <c r="E469" t="s" s="2">
@@ -57937,19 +57945,19 @@
         <v>102</v>
       </c>
       <c r="L469" t="s" s="2">
+        <v>1170</v>
+      </c>
+      <c r="M469" t="s" s="2">
         <v>1171</v>
       </c>
-      <c r="M469" t="s" s="2">
+      <c r="N469" t="s" s="2">
         <v>1172</v>
       </c>
-      <c r="N469" t="s" s="2">
+      <c r="O469" t="s" s="2">
         <v>1173</v>
       </c>
-      <c r="O469" t="s" s="2">
+      <c r="P469" t="s" s="2">
         <v>1174</v>
-      </c>
-      <c r="P469" t="s" s="2">
-        <v>1175</v>
       </c>
       <c r="Q469" t="s" s="2">
         <v>75</v>
@@ -57998,7 +58006,7 @@
         <v>75</v>
       </c>
       <c r="AG469" t="s" s="2">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="AH469" t="s" s="2">
         <v>76</v>
@@ -58007,7 +58015,7 @@
         <v>85</v>
       </c>
       <c r="AJ469" t="s" s="2">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="AK469" t="s" s="2">
         <v>107</v>
@@ -58015,13 +58023,13 @@
     </row>
     <row r="470">
       <c r="A470" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D470" s="2"/>
       <c r="E470" t="s" s="2">
@@ -58047,16 +58055,16 @@
         <v>229</v>
       </c>
       <c r="M470" t="s" s="2">
+        <v>1177</v>
+      </c>
+      <c r="N470" t="s" s="2">
         <v>1178</v>
       </c>
-      <c r="N470" t="s" s="2">
+      <c r="O470" t="s" s="2">
         <v>1179</v>
       </c>
-      <c r="O470" t="s" s="2">
+      <c r="P470" t="s" s="2">
         <v>1180</v>
-      </c>
-      <c r="P470" t="s" s="2">
-        <v>1181</v>
       </c>
       <c r="Q470" t="s" s="2">
         <v>75</v>
@@ -58084,37 +58092,37 @@
         <v>318</v>
       </c>
       <c r="Z470" t="s" s="2">
+        <v>1181</v>
+      </c>
+      <c r="AA470" t="s" s="2">
         <v>1182</v>
       </c>
-      <c r="AA470" t="s" s="2">
+      <c r="AB470" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC470" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD470" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE470" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF470" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG470" t="s" s="2">
+        <v>1176</v>
+      </c>
+      <c r="AH470" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI470" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ470" t="s" s="2">
         <v>1183</v>
-      </c>
-      <c r="AB470" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC470" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD470" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE470" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF470" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG470" t="s" s="2">
-        <v>1177</v>
-      </c>
-      <c r="AH470" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI470" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ470" t="s" s="2">
-        <v>1184</v>
       </c>
       <c r="AK470" t="s" s="2">
         <v>107</v>
@@ -58122,17 +58130,17 @@
     </row>
     <row r="471">
       <c r="A471" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D471" s="2"/>
       <c r="E471" t="s" s="2">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="F471" s="2"/>
       <c r="G471" t="s" s="2">
@@ -58154,16 +58162,16 @@
         <v>229</v>
       </c>
       <c r="M471" t="s" s="2">
+        <v>1186</v>
+      </c>
+      <c r="N471" t="s" s="2">
         <v>1187</v>
       </c>
-      <c r="N471" t="s" s="2">
+      <c r="O471" t="s" s="2">
         <v>1188</v>
       </c>
-      <c r="O471" t="s" s="2">
+      <c r="P471" t="s" s="2">
         <v>1189</v>
-      </c>
-      <c r="P471" t="s" s="2">
-        <v>1190</v>
       </c>
       <c r="Q471" t="s" s="2">
         <v>75</v>
@@ -58191,11 +58199,11 @@
         <v>318</v>
       </c>
       <c r="Z471" t="s" s="2">
+        <v>1190</v>
+      </c>
+      <c r="AA471" t="s" s="2">
         <v>1191</v>
       </c>
-      <c r="AA471" t="s" s="2">
-        <v>1192</v>
-      </c>
       <c r="AB471" t="s" s="2">
         <v>75</v>
       </c>
@@ -58212,7 +58220,7 @@
         <v>75</v>
       </c>
       <c r="AG471" t="s" s="2">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="AH471" t="s" s="2">
         <v>76</v>
@@ -58229,13 +58237,13 @@
     </row>
     <row r="472">
       <c r="A472" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="D472" s="2"/>
       <c r="E472" t="s" s="2">
@@ -58261,16 +58269,16 @@
         <v>506</v>
       </c>
       <c r="M472" t="s" s="2">
+        <v>1193</v>
+      </c>
+      <c r="N472" t="s" s="2">
         <v>1194</v>
       </c>
-      <c r="N472" t="s" s="2">
+      <c r="O472" t="s" s="2">
         <v>1195</v>
       </c>
-      <c r="O472" t="s" s="2">
+      <c r="P472" t="s" s="2">
         <v>1196</v>
-      </c>
-      <c r="P472" t="s" s="2">
-        <v>1197</v>
       </c>
       <c r="Q472" t="s" s="2">
         <v>75</v>
@@ -58319,7 +58327,7 @@
         <v>75</v>
       </c>
       <c r="AG472" t="s" s="2">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="AH472" t="s" s="2">
         <v>76</v>
@@ -58336,13 +58344,13 @@
     </row>
     <row r="473">
       <c r="A473" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D473" s="2"/>
       <c r="E473" t="s" s="2">
@@ -58368,13 +58376,13 @@
         <v>229</v>
       </c>
       <c r="M473" t="s" s="2">
+        <v>1198</v>
+      </c>
+      <c r="N473" t="s" s="2">
         <v>1199</v>
       </c>
-      <c r="N473" t="s" s="2">
+      <c r="O473" t="s" s="2">
         <v>1200</v>
-      </c>
-      <c r="O473" t="s" s="2">
-        <v>1201</v>
       </c>
       <c r="P473" s="2"/>
       <c r="Q473" t="s" s="2">
@@ -58403,11 +58411,11 @@
         <v>232</v>
       </c>
       <c r="Z473" t="s" s="2">
+        <v>1201</v>
+      </c>
+      <c r="AA473" t="s" s="2">
         <v>1202</v>
       </c>
-      <c r="AA473" t="s" s="2">
-        <v>1203</v>
-      </c>
       <c r="AB473" t="s" s="2">
         <v>75</v>
       </c>
@@ -58424,7 +58432,7 @@
         <v>75</v>
       </c>
       <c r="AG473" t="s" s="2">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="AH473" t="s" s="2">
         <v>76</v>
@@ -58441,13 +58449,13 @@
     </row>
     <row r="474">
       <c r="A474" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D474" s="2"/>
       <c r="E474" t="s" s="2">
@@ -58473,16 +58481,16 @@
         <v>229</v>
       </c>
       <c r="M474" t="s" s="2">
+        <v>1204</v>
+      </c>
+      <c r="N474" t="s" s="2">
         <v>1205</v>
       </c>
-      <c r="N474" t="s" s="2">
+      <c r="O474" t="s" s="2">
         <v>1206</v>
       </c>
-      <c r="O474" t="s" s="2">
+      <c r="P474" t="s" s="2">
         <v>1207</v>
-      </c>
-      <c r="P474" t="s" s="2">
-        <v>1208</v>
       </c>
       <c r="Q474" t="s" s="2">
         <v>75</v>
@@ -58510,11 +58518,11 @@
         <v>232</v>
       </c>
       <c r="Z474" t="s" s="2">
+        <v>1208</v>
+      </c>
+      <c r="AA474" t="s" s="2">
         <v>1209</v>
       </c>
-      <c r="AA474" t="s" s="2">
-        <v>1210</v>
-      </c>
       <c r="AB474" t="s" s="2">
         <v>75</v>
       </c>
@@ -58531,7 +58539,7 @@
         <v>75</v>
       </c>
       <c r="AG474" t="s" s="2">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="AH474" t="s" s="2">
         <v>76</v>
@@ -58548,13 +58556,13 @@
     </row>
     <row r="475">
       <c r="A475" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="D475" s="2"/>
       <c r="E475" t="s" s="2">
@@ -58577,16 +58585,16 @@
         <v>75</v>
       </c>
       <c r="L475" t="s" s="2">
+        <v>1211</v>
+      </c>
+      <c r="M475" t="s" s="2">
         <v>1212</v>
       </c>
-      <c r="M475" t="s" s="2">
+      <c r="N475" t="s" s="2">
         <v>1213</v>
       </c>
-      <c r="N475" t="s" s="2">
+      <c r="O475" t="s" s="2">
         <v>1214</v>
-      </c>
-      <c r="O475" t="s" s="2">
-        <v>1215</v>
       </c>
       <c r="P475" s="2"/>
       <c r="Q475" t="s" s="2">
@@ -58636,7 +58644,7 @@
         <v>75</v>
       </c>
       <c r="AG475" t="s" s="2">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="AH475" t="s" s="2">
         <v>76</v>
@@ -58653,13 +58661,13 @@
     </row>
     <row r="476">
       <c r="A476" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D476" s="2"/>
       <c r="E476" t="s" s="2">
@@ -58682,16 +58690,16 @@
         <v>75</v>
       </c>
       <c r="L476" t="s" s="2">
+        <v>1216</v>
+      </c>
+      <c r="M476" t="s" s="2">
         <v>1217</v>
       </c>
-      <c r="M476" t="s" s="2">
+      <c r="N476" t="s" s="2">
         <v>1218</v>
       </c>
-      <c r="N476" t="s" s="2">
+      <c r="O476" t="s" s="2">
         <v>1219</v>
-      </c>
-      <c r="O476" t="s" s="2">
-        <v>1220</v>
       </c>
       <c r="P476" s="2"/>
       <c r="Q476" t="s" s="2">
@@ -58741,7 +58749,7 @@
         <v>75</v>
       </c>
       <c r="AG476" t="s" s="2">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="AH476" t="s" s="2">
         <v>76</v>
@@ -58758,13 +58766,13 @@
     </row>
     <row r="477">
       <c r="A477" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D477" s="2"/>
       <c r="E477" t="s" s="2">
@@ -58790,16 +58798,16 @@
         <v>772</v>
       </c>
       <c r="M477" t="s" s="2">
+        <v>1221</v>
+      </c>
+      <c r="N477" t="s" s="2">
         <v>1222</v>
       </c>
-      <c r="N477" t="s" s="2">
+      <c r="O477" t="s" s="2">
         <v>1223</v>
       </c>
-      <c r="O477" t="s" s="2">
+      <c r="P477" t="s" s="2">
         <v>1224</v>
-      </c>
-      <c r="P477" t="s" s="2">
-        <v>1225</v>
       </c>
       <c r="Q477" t="s" s="2">
         <v>75</v>
@@ -58848,7 +58856,7 @@
         <v>75</v>
       </c>
       <c r="AG477" t="s" s="2">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="AH477" t="s" s="2">
         <v>76</v>
@@ -58860,18 +58868,18 @@
         <v>75</v>
       </c>
       <c r="AK477" t="s" s="2">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D478" s="2"/>
       <c r="E478" t="s" s="2">
@@ -58968,13 +58976,13 @@
     </row>
     <row r="479">
       <c r="A479" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" t="s" s="2">
@@ -59073,13 +59081,13 @@
     </row>
     <row r="480">
       <c r="A480" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D480" s="2"/>
       <c r="E480" t="s" s="2">
@@ -59180,13 +59188,13 @@
     </row>
     <row r="481">
       <c r="A481" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" t="s" s="2">
@@ -59212,10 +59220,10 @@
         <v>786</v>
       </c>
       <c r="M481" t="s" s="2">
+        <v>1230</v>
+      </c>
+      <c r="N481" t="s" s="2">
         <v>1231</v>
-      </c>
-      <c r="N481" t="s" s="2">
-        <v>1232</v>
       </c>
       <c r="O481" s="2"/>
       <c r="P481" s="2"/>
@@ -59266,7 +59274,7 @@
         <v>75</v>
       </c>
       <c r="AG481" t="s" s="2">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="AH481" t="s" s="2">
         <v>76</v>
@@ -59275,7 +59283,7 @@
         <v>85</v>
       </c>
       <c r="AJ481" t="s" s="2">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="AK481" t="s" s="2">
         <v>107</v>
@@ -59283,13 +59291,13 @@
     </row>
     <row r="482">
       <c r="A482" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="D482" s="2"/>
       <c r="E482" t="s" s="2">
@@ -59315,10 +59323,10 @@
         <v>786</v>
       </c>
       <c r="M482" t="s" s="2">
+        <v>1234</v>
+      </c>
+      <c r="N482" t="s" s="2">
         <v>1235</v>
-      </c>
-      <c r="N482" t="s" s="2">
-        <v>1236</v>
       </c>
       <c r="O482" s="2"/>
       <c r="P482" s="2"/>
@@ -59369,7 +59377,7 @@
         <v>75</v>
       </c>
       <c r="AG482" t="s" s="2">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="AH482" t="s" s="2">
         <v>76</v>
@@ -59378,7 +59386,7 @@
         <v>85</v>
       </c>
       <c r="AJ482" t="s" s="2">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="AK482" t="s" s="2">
         <v>107</v>
@@ -59386,13 +59394,13 @@
     </row>
     <row r="483">
       <c r="A483" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="D483" s="2"/>
       <c r="E483" t="s" s="2">
@@ -59418,16 +59426,16 @@
         <v>229</v>
       </c>
       <c r="M483" t="s" s="2">
+        <v>1237</v>
+      </c>
+      <c r="N483" t="s" s="2">
         <v>1238</v>
       </c>
-      <c r="N483" t="s" s="2">
+      <c r="O483" t="s" s="2">
         <v>1239</v>
       </c>
-      <c r="O483" t="s" s="2">
+      <c r="P483" t="s" s="2">
         <v>1240</v>
-      </c>
-      <c r="P483" t="s" s="2">
-        <v>1241</v>
       </c>
       <c r="Q483" t="s" s="2">
         <v>75</v>
@@ -59455,11 +59463,11 @@
         <v>276</v>
       </c>
       <c r="Z483" t="s" s="2">
+        <v>1241</v>
+      </c>
+      <c r="AA483" t="s" s="2">
         <v>1242</v>
       </c>
-      <c r="AA483" t="s" s="2">
-        <v>1243</v>
-      </c>
       <c r="AB483" t="s" s="2">
         <v>75</v>
       </c>
@@ -59476,7 +59484,7 @@
         <v>75</v>
       </c>
       <c r="AG483" t="s" s="2">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="AH483" t="s" s="2">
         <v>76</v>
@@ -59493,13 +59501,13 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="D484" s="2"/>
       <c r="E484" t="s" s="2">
@@ -59525,16 +59533,16 @@
         <v>229</v>
       </c>
       <c r="M484" t="s" s="2">
+        <v>1244</v>
+      </c>
+      <c r="N484" t="s" s="2">
         <v>1245</v>
       </c>
-      <c r="N484" t="s" s="2">
+      <c r="O484" t="s" s="2">
         <v>1246</v>
       </c>
-      <c r="O484" t="s" s="2">
+      <c r="P484" t="s" s="2">
         <v>1247</v>
-      </c>
-      <c r="P484" t="s" s="2">
-        <v>1248</v>
       </c>
       <c r="Q484" t="s" s="2">
         <v>75</v>
@@ -59562,11 +59570,11 @@
         <v>232</v>
       </c>
       <c r="Z484" t="s" s="2">
+        <v>1248</v>
+      </c>
+      <c r="AA484" t="s" s="2">
         <v>1249</v>
       </c>
-      <c r="AA484" t="s" s="2">
-        <v>1250</v>
-      </c>
       <c r="AB484" t="s" s="2">
         <v>75</v>
       </c>
@@ -59583,7 +59591,7 @@
         <v>75</v>
       </c>
       <c r="AG484" t="s" s="2">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="AH484" t="s" s="2">
         <v>76</v>
@@ -59600,13 +59608,13 @@
     </row>
     <row r="485">
       <c r="A485" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="D485" s="2"/>
       <c r="E485" t="s" s="2">
@@ -59629,17 +59637,17 @@
         <v>75</v>
       </c>
       <c r="L485" t="s" s="2">
+        <v>1251</v>
+      </c>
+      <c r="M485" t="s" s="2">
         <v>1252</v>
       </c>
-      <c r="M485" t="s" s="2">
+      <c r="N485" t="s" s="2">
         <v>1253</v>
-      </c>
-      <c r="N485" t="s" s="2">
-        <v>1254</v>
       </c>
       <c r="O485" s="2"/>
       <c r="P485" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="Q485" t="s" s="2">
         <v>75</v>
@@ -59688,7 +59696,7 @@
         <v>75</v>
       </c>
       <c r="AG485" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="AH485" t="s" s="2">
         <v>76</v>
@@ -59705,13 +59713,13 @@
     </row>
     <row r="486">
       <c r="A486" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="D486" s="2"/>
       <c r="E486" t="s" s="2">
@@ -59737,10 +59745,10 @@
         <v>86</v>
       </c>
       <c r="M486" t="s" s="2">
+        <v>1256</v>
+      </c>
+      <c r="N486" t="s" s="2">
         <v>1257</v>
-      </c>
-      <c r="N486" t="s" s="2">
-        <v>1258</v>
       </c>
       <c r="O486" s="2"/>
       <c r="P486" s="2"/>
@@ -59791,7 +59799,7 @@
         <v>75</v>
       </c>
       <c r="AG486" t="s" s="2">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="AH486" t="s" s="2">
         <v>76</v>
@@ -59808,13 +59816,13 @@
     </row>
     <row r="487">
       <c r="A487" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" t="s" s="2">
@@ -59837,16 +59845,16 @@
         <v>102</v>
       </c>
       <c r="L487" t="s" s="2">
+        <v>1259</v>
+      </c>
+      <c r="M487" t="s" s="2">
         <v>1260</v>
       </c>
-      <c r="M487" t="s" s="2">
+      <c r="N487" t="s" s="2">
         <v>1261</v>
       </c>
-      <c r="N487" t="s" s="2">
+      <c r="O487" t="s" s="2">
         <v>1262</v>
-      </c>
-      <c r="O487" t="s" s="2">
-        <v>1263</v>
       </c>
       <c r="P487" s="2"/>
       <c r="Q487" t="s" s="2">
@@ -59896,7 +59904,7 @@
         <v>75</v>
       </c>
       <c r="AG487" t="s" s="2">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="AH487" t="s" s="2">
         <v>76</v>
@@ -59913,13 +59921,13 @@
     </row>
     <row r="488">
       <c r="A488" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" t="s" s="2">
@@ -59942,16 +59950,16 @@
         <v>102</v>
       </c>
       <c r="L488" t="s" s="2">
+        <v>1264</v>
+      </c>
+      <c r="M488" t="s" s="2">
         <v>1265</v>
       </c>
-      <c r="M488" t="s" s="2">
+      <c r="N488" t="s" s="2">
         <v>1266</v>
       </c>
-      <c r="N488" t="s" s="2">
+      <c r="O488" t="s" s="2">
         <v>1267</v>
-      </c>
-      <c r="O488" t="s" s="2">
-        <v>1268</v>
       </c>
       <c r="P488" s="2"/>
       <c r="Q488" t="s" s="2">
@@ -60001,7 +60009,7 @@
         <v>75</v>
       </c>
       <c r="AG488" t="s" s="2">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="AH488" t="s" s="2">
         <v>76</v>
@@ -60018,13 +60026,13 @@
     </row>
     <row r="489">
       <c r="A489" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="D489" s="2"/>
       <c r="E489" t="s" s="2">
@@ -60050,16 +60058,16 @@
         <v>772</v>
       </c>
       <c r="M489" t="s" s="2">
+        <v>1269</v>
+      </c>
+      <c r="N489" t="s" s="2">
         <v>1270</v>
       </c>
-      <c r="N489" t="s" s="2">
+      <c r="O489" t="s" s="2">
         <v>1271</v>
       </c>
-      <c r="O489" t="s" s="2">
+      <c r="P489" t="s" s="2">
         <v>1272</v>
-      </c>
-      <c r="P489" t="s" s="2">
-        <v>1273</v>
       </c>
       <c r="Q489" t="s" s="2">
         <v>75</v>
@@ -60108,7 +60116,7 @@
         <v>75</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>76</v>
@@ -60125,13 +60133,13 @@
     </row>
     <row r="490">
       <c r="A490" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D490" s="2"/>
       <c r="E490" t="s" s="2">
@@ -60228,13 +60236,13 @@
     </row>
     <row r="491">
       <c r="A491" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D491" s="2"/>
       <c r="E491" t="s" s="2">
@@ -60333,13 +60341,13 @@
     </row>
     <row r="492">
       <c r="A492" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
@@ -60440,13 +60448,13 @@
     </row>
     <row r="493">
       <c r="A493" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -60472,16 +60480,16 @@
         <v>229</v>
       </c>
       <c r="M493" t="s" s="2">
+        <v>1277</v>
+      </c>
+      <c r="N493" t="s" s="2">
         <v>1278</v>
       </c>
-      <c r="N493" t="s" s="2">
+      <c r="O493" t="s" s="2">
         <v>1279</v>
       </c>
-      <c r="O493" t="s" s="2">
-        <v>1280</v>
-      </c>
       <c r="P493" t="s" s="2">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="Q493" t="s" s="2">
         <v>75</v>
@@ -60509,11 +60517,11 @@
         <v>232</v>
       </c>
       <c r="Z493" t="s" s="2">
+        <v>1134</v>
+      </c>
+      <c r="AA493" t="s" s="2">
         <v>1135</v>
       </c>
-      <c r="AA493" t="s" s="2">
-        <v>1136</v>
-      </c>
       <c r="AB493" t="s" s="2">
         <v>75</v>
       </c>
@@ -60530,7 +60538,7 @@
         <v>75</v>
       </c>
       <c r="AG493" t="s" s="2">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="AH493" t="s" s="2">
         <v>85</v>
@@ -60547,13 +60555,13 @@
     </row>
     <row r="494">
       <c r="A494" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -60576,19 +60584,19 @@
         <v>102</v>
       </c>
       <c r="L494" t="s" s="2">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="M494" t="s" s="2">
+        <v>1281</v>
+      </c>
+      <c r="N494" t="s" s="2">
+        <v>1172</v>
+      </c>
+      <c r="O494" t="s" s="2">
         <v>1282</v>
       </c>
-      <c r="N494" t="s" s="2">
-        <v>1173</v>
-      </c>
-      <c r="O494" t="s" s="2">
-        <v>1283</v>
-      </c>
       <c r="P494" t="s" s="2">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="Q494" t="s" s="2">
         <v>75</v>
@@ -60637,7 +60645,7 @@
         <v>75</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>76</v>
@@ -60654,13 +60662,13 @@
     </row>
     <row r="495">
       <c r="A495" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -60686,16 +60694,16 @@
         <v>229</v>
       </c>
       <c r="M495" t="s" s="2">
+        <v>1284</v>
+      </c>
+      <c r="N495" t="s" s="2">
         <v>1285</v>
       </c>
-      <c r="N495" t="s" s="2">
+      <c r="O495" t="s" s="2">
         <v>1286</v>
       </c>
-      <c r="O495" t="s" s="2">
-        <v>1287</v>
-      </c>
       <c r="P495" t="s" s="2">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="Q495" t="s" s="2">
         <v>75</v>
@@ -60723,37 +60731,37 @@
         <v>318</v>
       </c>
       <c r="Z495" t="s" s="2">
+        <v>1181</v>
+      </c>
+      <c r="AA495" t="s" s="2">
         <v>1182</v>
       </c>
-      <c r="AA495" t="s" s="2">
+      <c r="AB495" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC495" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD495" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE495" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF495" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AG495" t="s" s="2">
+        <v>1283</v>
+      </c>
+      <c r="AH495" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI495" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ495" t="s" s="2">
         <v>1183</v>
-      </c>
-      <c r="AB495" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC495" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD495" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE495" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF495" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AG495" t="s" s="2">
-        <v>1284</v>
-      </c>
-      <c r="AH495" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI495" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ495" t="s" s="2">
-        <v>1184</v>
       </c>
       <c r="AK495" t="s" s="2">
         <v>107</v>
@@ -60761,17 +60769,17 @@
     </row>
     <row r="496">
       <c r="A496" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D496" s="2"/>
       <c r="E496" t="s" s="2">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="F496" s="2"/>
       <c r="G496" t="s" s="2">
@@ -60793,16 +60801,16 @@
         <v>229</v>
       </c>
       <c r="M496" t="s" s="2">
+        <v>1186</v>
+      </c>
+      <c r="N496" t="s" s="2">
         <v>1187</v>
       </c>
-      <c r="N496" t="s" s="2">
+      <c r="O496" t="s" s="2">
         <v>1188</v>
       </c>
-      <c r="O496" t="s" s="2">
+      <c r="P496" t="s" s="2">
         <v>1189</v>
-      </c>
-      <c r="P496" t="s" s="2">
-        <v>1190</v>
       </c>
       <c r="Q496" t="s" s="2">
         <v>75</v>
@@ -60830,11 +60838,11 @@
         <v>318</v>
       </c>
       <c r="Z496" t="s" s="2">
+        <v>1190</v>
+      </c>
+      <c r="AA496" t="s" s="2">
         <v>1191</v>
       </c>
-      <c r="AA496" t="s" s="2">
-        <v>1192</v>
-      </c>
       <c r="AB496" t="s" s="2">
         <v>75</v>
       </c>
@@ -60851,7 +60859,7 @@
         <v>75</v>
       </c>
       <c r="AG496" t="s" s="2">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="AH496" t="s" s="2">
         <v>76</v>
@@ -60868,13 +60876,13 @@
     </row>
     <row r="497">
       <c r="A497" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
@@ -60900,16 +60908,16 @@
         <v>78</v>
       </c>
       <c r="M497" t="s" s="2">
+        <v>1289</v>
+      </c>
+      <c r="N497" t="s" s="2">
         <v>1290</v>
       </c>
-      <c r="N497" t="s" s="2">
-        <v>1291</v>
-      </c>
       <c r="O497" t="s" s="2">
+        <v>1223</v>
+      </c>
+      <c r="P497" t="s" s="2">
         <v>1224</v>
-      </c>
-      <c r="P497" t="s" s="2">
-        <v>1225</v>
       </c>
       <c r="Q497" t="s" s="2">
         <v>75</v>
@@ -60958,7 +60966,7 @@
         <v>75</v>
       </c>
       <c r="AG497" t="s" s="2">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="AH497" t="s" s="2">
         <v>76</v>
@@ -60975,13 +60983,13 @@
     </row>
     <row r="498">
       <c r="A498" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
@@ -61007,10 +61015,10 @@
         <v>78</v>
       </c>
       <c r="M498" t="s" s="2">
+        <v>1299</v>
+      </c>
+      <c r="N498" t="s" s="2">
         <v>1300</v>
-      </c>
-      <c r="N498" t="s" s="2">
-        <v>1301</v>
       </c>
       <c r="O498" s="2"/>
       <c r="P498" s="2"/>
@@ -61061,7 +61069,7 @@
         <v>75</v>
       </c>
       <c r="AG498" t="s" s="2">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="AH498" t="s" s="2">
         <v>76</v>
@@ -61073,18 +61081,18 @@
         <v>75</v>
       </c>
       <c r="AK498" t="s" s="2">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
@@ -61183,13 +61191,13 @@
     </row>
     <row r="500">
       <c r="A500" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
@@ -61286,13 +61294,13 @@
     </row>
     <row r="501">
       <c r="A501" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
@@ -61391,13 +61399,13 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
@@ -61496,13 +61504,13 @@
     </row>
     <row r="503">
       <c r="A503" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -61528,13 +61536,13 @@
         <v>346</v>
       </c>
       <c r="M503" t="s" s="2">
+        <v>1307</v>
+      </c>
+      <c r="N503" t="s" s="2">
         <v>1308</v>
       </c>
-      <c r="N503" t="s" s="2">
+      <c r="O503" t="s" s="2">
         <v>1309</v>
-      </c>
-      <c r="O503" t="s" s="2">
-        <v>1310</v>
       </c>
       <c r="P503" s="2"/>
       <c r="Q503" t="s" s="2">
@@ -61584,7 +61592,7 @@
         <v>75</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>76</v>
@@ -61601,13 +61609,13 @@
     </row>
     <row r="504">
       <c r="A504" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
@@ -61633,13 +61641,13 @@
         <v>149</v>
       </c>
       <c r="M504" t="s" s="2">
+        <v>1311</v>
+      </c>
+      <c r="N504" t="s" s="2">
         <v>1312</v>
       </c>
-      <c r="N504" t="s" s="2">
+      <c r="O504" t="s" s="2">
         <v>1313</v>
-      </c>
-      <c r="O504" t="s" s="2">
-        <v>1314</v>
       </c>
       <c r="P504" s="2"/>
       <c r="Q504" t="s" s="2">
@@ -61668,11 +61676,11 @@
         <v>154</v>
       </c>
       <c r="Z504" t="s" s="2">
+        <v>1314</v>
+      </c>
+      <c r="AA504" t="s" s="2">
         <v>1315</v>
       </c>
-      <c r="AA504" t="s" s="2">
-        <v>1316</v>
-      </c>
       <c r="AB504" t="s" s="2">
         <v>75</v>
       </c>
@@ -61689,7 +61697,7 @@
         <v>75</v>
       </c>
       <c r="AG504" t="s" s="2">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="AH504" t="s" s="2">
         <v>85</v>
@@ -61706,13 +61714,13 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
@@ -61735,16 +61743,16 @@
         <v>102</v>
       </c>
       <c r="L505" t="s" s="2">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="M505" t="s" s="2">
+        <v>1317</v>
+      </c>
+      <c r="N505" t="s" s="2">
         <v>1318</v>
       </c>
-      <c r="N505" t="s" s="2">
+      <c r="O505" t="s" s="2">
         <v>1319</v>
-      </c>
-      <c r="O505" t="s" s="2">
-        <v>1320</v>
       </c>
       <c r="P505" s="2"/>
       <c r="Q505" t="s" s="2">
@@ -61794,7 +61802,7 @@
         <v>75</v>
       </c>
       <c r="AG505" t="s" s="2">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="AH505" t="s" s="2">
         <v>76</v>
@@ -61811,13 +61819,13 @@
     </row>
     <row r="506">
       <c r="A506" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
@@ -61843,13 +61851,13 @@
         <v>666</v>
       </c>
       <c r="M506" t="s" s="2">
+        <v>1321</v>
+      </c>
+      <c r="N506" t="s" s="2">
         <v>1322</v>
       </c>
-      <c r="N506" t="s" s="2">
+      <c r="O506" t="s" s="2">
         <v>1323</v>
-      </c>
-      <c r="O506" t="s" s="2">
-        <v>1324</v>
       </c>
       <c r="P506" s="2"/>
       <c r="Q506" t="s" s="2">
@@ -61899,7 +61907,7 @@
         <v>75</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>76</v>
@@ -61908,7 +61916,7 @@
         <v>85</v>
       </c>
       <c r="AJ506" t="s" s="2">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="AK506" t="s" s="2">
         <v>107</v>
@@ -61916,13 +61924,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -61948,13 +61956,13 @@
         <v>772</v>
       </c>
       <c r="M507" t="s" s="2">
+        <v>1326</v>
+      </c>
+      <c r="N507" t="s" s="2">
         <v>1327</v>
       </c>
-      <c r="N507" t="s" s="2">
+      <c r="O507" t="s" s="2">
         <v>1328</v>
-      </c>
-      <c r="O507" t="s" s="2">
-        <v>1329</v>
       </c>
       <c r="P507" s="2"/>
       <c r="Q507" t="s" s="2">
@@ -62004,7 +62012,7 @@
         <v>75</v>
       </c>
       <c r="AG507" t="s" s="2">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="AH507" t="s" s="2">
         <v>76</v>
@@ -62021,13 +62029,13 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -62124,13 +62132,13 @@
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
@@ -62229,13 +62237,13 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -62336,13 +62344,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -62368,10 +62376,10 @@
         <v>86</v>
       </c>
       <c r="M511" t="s" s="2">
+        <v>1333</v>
+      </c>
+      <c r="N511" t="s" s="2">
         <v>1334</v>
-      </c>
-      <c r="N511" t="s" s="2">
-        <v>1335</v>
       </c>
       <c r="O511" s="2"/>
       <c r="P511" s="2"/>
@@ -62422,7 +62430,7 @@
         <v>75</v>
       </c>
       <c r="AG511" t="s" s="2">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="AH511" t="s" s="2">
         <v>85</v>
@@ -62439,13 +62447,13 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -62471,10 +62479,10 @@
         <v>162</v>
       </c>
       <c r="M512" t="s" s="2">
+        <v>1336</v>
+      </c>
+      <c r="N512" t="s" s="2">
         <v>1337</v>
-      </c>
-      <c r="N512" t="s" s="2">
-        <v>1338</v>
       </c>
       <c r="O512" s="2"/>
       <c r="P512" s="2"/>
@@ -62525,7 +62533,7 @@
         <v>75</v>
       </c>
       <c r="AG512" t="s" s="2">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="AH512" t="s" s="2">
         <v>85</v>
@@ -62542,13 +62550,13 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -62574,10 +62582,10 @@
         <v>772</v>
       </c>
       <c r="M513" t="s" s="2">
+        <v>1339</v>
+      </c>
+      <c r="N513" t="s" s="2">
         <v>1340</v>
-      </c>
-      <c r="N513" t="s" s="2">
-        <v>1341</v>
       </c>
       <c r="O513" s="2"/>
       <c r="P513" s="2"/>
@@ -62628,7 +62636,7 @@
         <v>75</v>
       </c>
       <c r="AG513" t="s" s="2">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="AH513" t="s" s="2">
         <v>76</v>
@@ -62640,18 +62648,18 @@
         <v>75</v>
       </c>
       <c r="AK513" t="s" s="2">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -62748,13 +62756,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -62853,13 +62861,13 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -62960,13 +62968,13 @@
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -62992,10 +63000,10 @@
         <v>78</v>
       </c>
       <c r="M517" t="s" s="2">
+        <v>1346</v>
+      </c>
+      <c r="N517" t="s" s="2">
         <v>1347</v>
-      </c>
-      <c r="N517" t="s" s="2">
-        <v>1348</v>
       </c>
       <c r="O517" s="2"/>
       <c r="P517" s="2"/>
@@ -63046,7 +63054,7 @@
         <v>75</v>
       </c>
       <c r="AG517" t="s" s="2">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="AH517" t="s" s="2">
         <v>76</v>
@@ -63063,13 +63071,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -63095,13 +63103,13 @@
         <v>162</v>
       </c>
       <c r="M518" t="s" s="2">
+        <v>1349</v>
+      </c>
+      <c r="N518" t="s" s="2">
         <v>1350</v>
       </c>
-      <c r="N518" t="s" s="2">
+      <c r="O518" t="s" s="2">
         <v>1351</v>
-      </c>
-      <c r="O518" t="s" s="2">
-        <v>1352</v>
       </c>
       <c r="P518" s="2"/>
       <c r="Q518" t="s" s="2">
@@ -63151,7 +63159,7 @@
         <v>75</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>76</v>
@@ -63168,13 +63176,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -63200,10 +63208,10 @@
         <v>289</v>
       </c>
       <c r="M519" t="s" s="2">
+        <v>1353</v>
+      </c>
+      <c r="N519" t="s" s="2">
         <v>1354</v>
-      </c>
-      <c r="N519" t="s" s="2">
-        <v>1355</v>
       </c>
       <c r="O519" s="2"/>
       <c r="P519" s="2"/>
@@ -63254,7 +63262,7 @@
         <v>75</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="AH519" t="s" s="2">
         <v>76</v>
@@ -63271,13 +63279,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -63303,10 +63311,10 @@
         <v>772</v>
       </c>
       <c r="M520" t="s" s="2">
+        <v>1356</v>
+      </c>
+      <c r="N520" t="s" s="2">
         <v>1357</v>
-      </c>
-      <c r="N520" t="s" s="2">
-        <v>1358</v>
       </c>
       <c r="O520" s="2"/>
       <c r="P520" s="2"/>
@@ -63357,7 +63365,7 @@
         <v>75</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="AH520" t="s" s="2">
         <v>76</v>
@@ -63366,7 +63374,7 @@
         <v>85</v>
       </c>
       <c r="AJ520" t="s" s="2">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="AK520" t="s" s="2">
         <v>107</v>
@@ -63374,13 +63382,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -63477,13 +63485,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -63582,13 +63590,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -63689,13 +63697,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -63721,13 +63729,13 @@
         <v>149</v>
       </c>
       <c r="M524" t="s" s="2">
+        <v>1363</v>
+      </c>
+      <c r="N524" t="s" s="2">
         <v>1364</v>
       </c>
-      <c r="N524" t="s" s="2">
+      <c r="O524" t="s" s="2">
         <v>1365</v>
-      </c>
-      <c r="O524" t="s" s="2">
-        <v>1366</v>
       </c>
       <c r="P524" s="2"/>
       <c r="Q524" t="s" s="2">
@@ -63756,11 +63764,11 @@
         <v>154</v>
       </c>
       <c r="Z524" t="s" s="2">
+        <v>1366</v>
+      </c>
+      <c r="AA524" t="s" s="2">
         <v>1367</v>
       </c>
-      <c r="AA524" t="s" s="2">
-        <v>1368</v>
-      </c>
       <c r="AB524" t="s" s="2">
         <v>75</v>
       </c>
@@ -63777,7 +63785,7 @@
         <v>75</v>
       </c>
       <c r="AG524" t="s" s="2">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="AH524" t="s" s="2">
         <v>76</v>
@@ -63794,13 +63802,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -63826,13 +63834,13 @@
         <v>143</v>
       </c>
       <c r="M525" t="s" s="2">
+        <v>1369</v>
+      </c>
+      <c r="N525" t="s" s="2">
         <v>1370</v>
       </c>
-      <c r="N525" t="s" s="2">
+      <c r="O525" t="s" s="2">
         <v>1371</v>
-      </c>
-      <c r="O525" t="s" s="2">
-        <v>1372</v>
       </c>
       <c r="P525" s="2"/>
       <c r="Q525" t="s" s="2">
@@ -63882,7 +63890,7 @@
         <v>75</v>
       </c>
       <c r="AG525" t="s" s="2">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="AH525" t="s" s="2">
         <v>76</v>
@@ -63899,13 +63907,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -63931,10 +63939,10 @@
         <v>772</v>
       </c>
       <c r="M526" t="s" s="2">
+        <v>1373</v>
+      </c>
+      <c r="N526" t="s" s="2">
         <v>1374</v>
-      </c>
-      <c r="N526" t="s" s="2">
-        <v>1375</v>
       </c>
       <c r="O526" s="2"/>
       <c r="P526" s="2"/>
@@ -63985,7 +63993,7 @@
         <v>75</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>76</v>
@@ -63994,7 +64002,7 @@
         <v>85</v>
       </c>
       <c r="AJ526" t="s" s="2">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="AK526" t="s" s="2">
         <v>107</v>
@@ -64002,13 +64010,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -64105,13 +64113,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -64210,13 +64218,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -64317,13 +64325,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -64349,10 +64357,10 @@
         <v>149</v>
       </c>
       <c r="M530" t="s" s="2">
+        <v>1380</v>
+      </c>
+      <c r="N530" t="s" s="2">
         <v>1381</v>
-      </c>
-      <c r="N530" t="s" s="2">
-        <v>1382</v>
       </c>
       <c r="O530" s="2"/>
       <c r="P530" s="2"/>
@@ -64382,11 +64390,11 @@
         <v>154</v>
       </c>
       <c r="Z530" t="s" s="2">
+        <v>1382</v>
+      </c>
+      <c r="AA530" t="s" s="2">
         <v>1383</v>
       </c>
-      <c r="AA530" t="s" s="2">
-        <v>1384</v>
-      </c>
       <c r="AB530" t="s" s="2">
         <v>75</v>
       </c>
@@ -64403,7 +64411,7 @@
         <v>75</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="AH530" t="s" s="2">
         <v>85</v>
@@ -64420,13 +64428,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -64452,13 +64460,13 @@
         <v>162</v>
       </c>
       <c r="M531" t="s" s="2">
+        <v>1385</v>
+      </c>
+      <c r="N531" t="s" s="2">
         <v>1386</v>
       </c>
-      <c r="N531" t="s" s="2">
+      <c r="O531" t="s" s="2">
         <v>1387</v>
-      </c>
-      <c r="O531" t="s" s="2">
-        <v>1388</v>
       </c>
       <c r="P531" s="2"/>
       <c r="Q531" t="s" s="2">
@@ -64508,7 +64516,7 @@
         <v>75</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>85</v>
@@ -64525,13 +64533,13 @@
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -64557,10 +64565,10 @@
         <v>86</v>
       </c>
       <c r="M532" t="s" s="2">
+        <v>1389</v>
+      </c>
+      <c r="N532" t="s" s="2">
         <v>1390</v>
-      </c>
-      <c r="N532" t="s" s="2">
-        <v>1391</v>
       </c>
       <c r="O532" s="2"/>
       <c r="P532" s="2"/>
@@ -64611,7 +64619,7 @@
         <v>75</v>
       </c>
       <c r="AG532" t="s" s="2">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="AH532" t="s" s="2">
         <v>76</v>
@@ -64628,13 +64636,13 @@
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -64657,13 +64665,13 @@
         <v>102</v>
       </c>
       <c r="L533" t="s" s="2">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="M533" t="s" s="2">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="N533" t="s" s="2">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="O533" s="2"/>
       <c r="P533" s="2"/>
@@ -64714,7 +64722,7 @@
         <v>75</v>
       </c>
       <c r="AG533" t="s" s="2">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="AH533" t="s" s="2">
         <v>76</v>
@@ -64731,13 +64739,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -64763,10 +64771,10 @@
         <v>86</v>
       </c>
       <c r="M534" t="s" s="2">
+        <v>1394</v>
+      </c>
+      <c r="N534" t="s" s="2">
         <v>1395</v>
-      </c>
-      <c r="N534" t="s" s="2">
-        <v>1396</v>
       </c>
       <c r="O534" s="2"/>
       <c r="P534" s="2"/>
@@ -64817,7 +64825,7 @@
         <v>75</v>
       </c>
       <c r="AG534" t="s" s="2">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="AH534" t="s" s="2">
         <v>76</v>
@@ -64834,13 +64842,13 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
@@ -64866,10 +64874,10 @@
         <v>86</v>
       </c>
       <c r="M535" t="s" s="2">
+        <v>1397</v>
+      </c>
+      <c r="N535" t="s" s="2">
         <v>1398</v>
-      </c>
-      <c r="N535" t="s" s="2">
-        <v>1399</v>
       </c>
       <c r="O535" s="2"/>
       <c r="P535" s="2"/>
@@ -64920,7 +64928,7 @@
         <v>75</v>
       </c>
       <c r="AG535" t="s" s="2">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="AH535" t="s" s="2">
         <v>76</v>
@@ -64937,13 +64945,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -64969,10 +64977,10 @@
         <v>772</v>
       </c>
       <c r="M536" t="s" s="2">
+        <v>1400</v>
+      </c>
+      <c r="N536" t="s" s="2">
         <v>1401</v>
-      </c>
-      <c r="N536" t="s" s="2">
-        <v>1402</v>
       </c>
       <c r="O536" s="2"/>
       <c r="P536" s="2"/>
@@ -65023,7 +65031,7 @@
         <v>75</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="AH536" t="s" s="2">
         <v>76</v>
@@ -65032,7 +65040,7 @@
         <v>85</v>
       </c>
       <c r="AJ536" t="s" s="2">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="AK536" t="s" s="2">
         <v>107</v>
@@ -65040,13 +65048,13 @@
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -65143,13 +65151,13 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
@@ -65248,13 +65256,13 @@
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -65355,13 +65363,13 @@
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
@@ -65387,10 +65395,10 @@
         <v>86</v>
       </c>
       <c r="M540" t="s" s="2">
+        <v>1407</v>
+      </c>
+      <c r="N540" t="s" s="2">
         <v>1408</v>
-      </c>
-      <c r="N540" t="s" s="2">
-        <v>1409</v>
       </c>
       <c r="O540" s="2"/>
       <c r="P540" s="2"/>
@@ -65441,7 +65449,7 @@
         <v>75</v>
       </c>
       <c r="AG540" t="s" s="2">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="AH540" t="s" s="2">
         <v>85</v>
@@ -65458,13 +65466,13 @@
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
@@ -65490,10 +65498,10 @@
         <v>162</v>
       </c>
       <c r="M541" t="s" s="2">
+        <v>1410</v>
+      </c>
+      <c r="N541" t="s" s="2">
         <v>1411</v>
-      </c>
-      <c r="N541" t="s" s="2">
-        <v>1412</v>
       </c>
       <c r="O541" s="2"/>
       <c r="P541" s="2"/>
@@ -65544,7 +65552,7 @@
         <v>75</v>
       </c>
       <c r="AG541" t="s" s="2">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="AH541" t="s" s="2">
         <v>76</v>
@@ -65561,13 +65569,13 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
@@ -65593,13 +65601,13 @@
         <v>86</v>
       </c>
       <c r="M542" t="s" s="2">
+        <v>1413</v>
+      </c>
+      <c r="N542" t="s" s="2">
         <v>1414</v>
       </c>
-      <c r="N542" t="s" s="2">
+      <c r="O542" t="s" s="2">
         <v>1415</v>
-      </c>
-      <c r="O542" t="s" s="2">
-        <v>1416</v>
       </c>
       <c r="P542" s="2"/>
       <c r="Q542" t="s" s="2">
@@ -65649,7 +65657,7 @@
         <v>75</v>
       </c>
       <c r="AG542" t="s" s="2">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="AH542" t="s" s="2">
         <v>76</v>
@@ -65666,13 +65674,13 @@
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="D543" s="2"/>
       <c r="E543" t="s" s="2">
@@ -65695,16 +65703,16 @@
         <v>102</v>
       </c>
       <c r="L543" t="s" s="2">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="M543" t="s" s="2">
+        <v>1417</v>
+      </c>
+      <c r="N543" t="s" s="2">
         <v>1418</v>
       </c>
-      <c r="N543" t="s" s="2">
+      <c r="O543" t="s" s="2">
         <v>1419</v>
-      </c>
-      <c r="O543" t="s" s="2">
-        <v>1420</v>
       </c>
       <c r="P543" s="2"/>
       <c r="Q543" t="s" s="2">
@@ -65754,7 +65762,7 @@
         <v>75</v>
       </c>
       <c r="AG543" t="s" s="2">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="AH543" t="s" s="2">
         <v>76</v>
@@ -65771,13 +65779,13 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
@@ -65803,13 +65811,13 @@
         <v>289</v>
       </c>
       <c r="M544" t="s" s="2">
+        <v>1421</v>
+      </c>
+      <c r="N544" t="s" s="2">
         <v>1422</v>
       </c>
-      <c r="N544" t="s" s="2">
+      <c r="O544" t="s" s="2">
         <v>1423</v>
-      </c>
-      <c r="O544" t="s" s="2">
-        <v>1424</v>
       </c>
       <c r="P544" s="2"/>
       <c r="Q544" t="s" s="2">
@@ -65859,7 +65867,7 @@
         <v>75</v>
       </c>
       <c r="AG544" t="s" s="2">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="AH544" t="s" s="2">
         <v>76</v>
@@ -65876,13 +65884,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
@@ -65905,19 +65913,19 @@
         <v>102</v>
       </c>
       <c r="L545" t="s" s="2">
+        <v>1425</v>
+      </c>
+      <c r="M545" t="s" s="2">
         <v>1426</v>
       </c>
-      <c r="M545" t="s" s="2">
+      <c r="N545" t="s" s="2">
         <v>1427</v>
       </c>
-      <c r="N545" t="s" s="2">
+      <c r="O545" t="s" s="2">
         <v>1428</v>
       </c>
-      <c r="O545" t="s" s="2">
+      <c r="P545" t="s" s="2">
         <v>1429</v>
-      </c>
-      <c r="P545" t="s" s="2">
-        <v>1430</v>
       </c>
       <c r="Q545" t="s" s="2">
         <v>75</v>
@@ -65966,7 +65974,7 @@
         <v>75</v>
       </c>
       <c r="AG545" t="s" s="2">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="AH545" t="s" s="2">
         <v>76</v>
@@ -65983,13 +65991,13 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
@@ -66015,10 +66023,10 @@
         <v>78</v>
       </c>
       <c r="M546" t="s" s="2">
+        <v>1437</v>
+      </c>
+      <c r="N546" t="s" s="2">
         <v>1438</v>
-      </c>
-      <c r="N546" t="s" s="2">
-        <v>1439</v>
       </c>
       <c r="O546" s="2"/>
       <c r="P546" s="2"/>
@@ -66069,7 +66077,7 @@
         <v>75</v>
       </c>
       <c r="AG546" t="s" s="2">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="AH546" t="s" s="2">
         <v>76</v>
@@ -66086,13 +66094,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -66191,13 +66199,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -66294,13 +66302,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -66399,13 +66407,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -66504,13 +66512,13 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -66609,13 +66617,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -66714,13 +66722,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -66819,13 +66827,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -66926,13 +66934,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -66958,14 +66966,14 @@
         <v>346</v>
       </c>
       <c r="M555" t="s" s="2">
+        <v>1448</v>
+      </c>
+      <c r="N555" t="s" s="2">
         <v>1449</v>
-      </c>
-      <c r="N555" t="s" s="2">
-        <v>1450</v>
       </c>
       <c r="O555" s="2"/>
       <c r="P555" t="s" s="2">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="Q555" t="s" s="2">
         <v>75</v>
@@ -67014,7 +67022,7 @@
         <v>75</v>
       </c>
       <c r="AG555" t="s" s="2">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="AH555" t="s" s="2">
         <v>76</v>
@@ -67031,13 +67039,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -67066,7 +67074,7 @@
         <v>482</v>
       </c>
       <c r="N556" t="s" s="2">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="O556" s="2"/>
       <c r="P556" s="2"/>
@@ -67117,7 +67125,7 @@
         <v>75</v>
       </c>
       <c r="AG556" t="s" s="2">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="AH556" t="s" s="2">
         <v>76</v>
@@ -67134,13 +67142,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -67169,7 +67177,7 @@
         <v>485</v>
       </c>
       <c r="N557" t="s" s="2">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="O557" s="2"/>
       <c r="P557" s="2"/>
@@ -67220,7 +67228,7 @@
         <v>75</v>
       </c>
       <c r="AG557" t="s" s="2">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>76</v>
@@ -67237,17 +67245,17 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="F558" s="2"/>
       <c r="G558" t="s" s="2">
@@ -67269,14 +67277,14 @@
         <v>414</v>
       </c>
       <c r="M558" t="s" s="2">
+        <v>1457</v>
+      </c>
+      <c r="N558" t="s" s="2">
         <v>1458</v>
-      </c>
-      <c r="N558" t="s" s="2">
-        <v>1459</v>
       </c>
       <c r="O558" s="2"/>
       <c r="P558" t="s" s="2">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="Q558" t="s" s="2">
         <v>75</v>
@@ -67325,7 +67333,7 @@
         <v>75</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>76</v>
@@ -67342,17 +67350,17 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="F559" s="2"/>
       <c r="G559" t="s" s="2">
@@ -67374,16 +67382,16 @@
         <v>414</v>
       </c>
       <c r="M559" t="s" s="2">
+        <v>1462</v>
+      </c>
+      <c r="N559" t="s" s="2">
         <v>1463</v>
       </c>
-      <c r="N559" t="s" s="2">
+      <c r="O559" t="s" s="2">
         <v>1464</v>
       </c>
-      <c r="O559" t="s" s="2">
+      <c r="P559" t="s" s="2">
         <v>1465</v>
-      </c>
-      <c r="P559" t="s" s="2">
-        <v>1466</v>
       </c>
       <c r="Q559" t="s" s="2">
         <v>75</v>
@@ -67432,7 +67440,7 @@
         <v>75</v>
       </c>
       <c r="AG559" t="s" s="2">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="AH559" t="s" s="2">
         <v>76</v>
@@ -67449,17 +67457,17 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="F560" s="2"/>
       <c r="G560" t="s" s="2">
@@ -67484,13 +67492,13 @@
         <v>492</v>
       </c>
       <c r="N560" t="s" s="2">
+        <v>1468</v>
+      </c>
+      <c r="O560" t="s" s="2">
         <v>1469</v>
       </c>
-      <c r="O560" t="s" s="2">
+      <c r="P560" t="s" s="2">
         <v>1470</v>
-      </c>
-      <c r="P560" t="s" s="2">
-        <v>1471</v>
       </c>
       <c r="Q560" t="s" s="2">
         <v>75</v>
@@ -67539,7 +67547,7 @@
         <v>75</v>
       </c>
       <c r="AG560" t="s" s="2">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="AH560" t="s" s="2">
         <v>76</v>
@@ -67556,13 +67564,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -67588,10 +67596,10 @@
         <v>149</v>
       </c>
       <c r="M561" t="s" s="2">
+        <v>1472</v>
+      </c>
+      <c r="N561" t="s" s="2">
         <v>1473</v>
-      </c>
-      <c r="N561" t="s" s="2">
-        <v>1474</v>
       </c>
       <c r="O561" s="2"/>
       <c r="P561" s="2"/>
@@ -67621,11 +67629,11 @@
         <v>154</v>
       </c>
       <c r="Z561" t="s" s="2">
+        <v>1474</v>
+      </c>
+      <c r="AA561" t="s" s="2">
         <v>1475</v>
       </c>
-      <c r="AA561" t="s" s="2">
-        <v>1476</v>
-      </c>
       <c r="AB561" t="s" s="2">
         <v>75</v>
       </c>
@@ -67642,7 +67650,7 @@
         <v>75</v>
       </c>
       <c r="AG561" t="s" s="2">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="AH561" t="s" s="2">
         <v>85</v>
@@ -67659,17 +67667,17 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="F562" s="2"/>
       <c r="G562" t="s" s="2">
@@ -67691,14 +67699,14 @@
         <v>149</v>
       </c>
       <c r="M562" t="s" s="2">
+        <v>1478</v>
+      </c>
+      <c r="N562" t="s" s="2">
         <v>1479</v>
-      </c>
-      <c r="N562" t="s" s="2">
-        <v>1480</v>
       </c>
       <c r="O562" s="2"/>
       <c r="P562" t="s" s="2">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="Q562" t="s" s="2">
         <v>75</v>
@@ -67726,11 +67734,11 @@
         <v>154</v>
       </c>
       <c r="Z562" t="s" s="2">
+        <v>1481</v>
+      </c>
+      <c r="AA562" t="s" s="2">
         <v>1482</v>
       </c>
-      <c r="AA562" t="s" s="2">
-        <v>1483</v>
-      </c>
       <c r="AB562" t="s" s="2">
         <v>75</v>
       </c>
@@ -67747,7 +67755,7 @@
         <v>75</v>
       </c>
       <c r="AG562" t="s" s="2">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="AH562" t="s" s="2">
         <v>85</v>
@@ -67764,13 +67772,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" t="s" s="2">
@@ -67799,7 +67807,7 @@
         <v>375</v>
       </c>
       <c r="N563" t="s" s="2">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="O563" s="2"/>
       <c r="P563" s="2"/>
@@ -67807,7 +67815,7 @@
         <v>75</v>
       </c>
       <c r="R563" t="s" s="2">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="S563" t="s" s="2">
         <v>75</v>
@@ -67852,7 +67860,7 @@
         <v>75</v>
       </c>
       <c r="AG563" t="s" s="2">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="AH563" t="s" s="2">
         <v>76</v>
@@ -67869,13 +67877,13 @@
     </row>
     <row r="564">
       <c r="A564" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="D564" s="2"/>
       <c r="E564" t="s" s="2">
@@ -67901,13 +67909,13 @@
         <v>229</v>
       </c>
       <c r="M564" t="s" s="2">
+        <v>1487</v>
+      </c>
+      <c r="N564" t="s" s="2">
         <v>1488</v>
       </c>
-      <c r="N564" t="s" s="2">
+      <c r="O564" t="s" s="2">
         <v>1489</v>
-      </c>
-      <c r="O564" t="s" s="2">
-        <v>1490</v>
       </c>
       <c r="P564" s="2"/>
       <c r="Q564" t="s" s="2">
@@ -67957,7 +67965,7 @@
         <v>75</v>
       </c>
       <c r="AG564" t="s" s="2">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="AH564" t="s" s="2">
         <v>76</v>
@@ -67974,13 +67982,13 @@
     </row>
     <row r="565">
       <c r="A565" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D565" s="2"/>
       <c r="E565" t="s" s="2">
@@ -68003,13 +68011,13 @@
         <v>75</v>
       </c>
       <c r="L565" t="s" s="2">
+        <v>1491</v>
+      </c>
+      <c r="M565" t="s" s="2">
         <v>1492</v>
       </c>
-      <c r="M565" t="s" s="2">
+      <c r="N565" t="s" s="2">
         <v>1493</v>
-      </c>
-      <c r="N565" t="s" s="2">
-        <v>1494</v>
       </c>
       <c r="O565" s="2"/>
       <c r="P565" s="2"/>
@@ -68060,7 +68068,7 @@
         <v>75</v>
       </c>
       <c r="AG565" t="s" s="2">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="AH565" t="s" s="2">
         <v>76</v>
@@ -68077,13 +68085,13 @@
     </row>
     <row r="566">
       <c r="A566" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="C566" t="s" s="2">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="D566" s="2"/>
       <c r="E566" t="s" s="2">
@@ -68106,13 +68114,13 @@
         <v>75</v>
       </c>
       <c r="L566" t="s" s="2">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="M566" t="s" s="2">
+        <v>1495</v>
+      </c>
+      <c r="N566" t="s" s="2">
         <v>1496</v>
-      </c>
-      <c r="N566" t="s" s="2">
-        <v>1497</v>
       </c>
       <c r="O566" s="2"/>
       <c r="P566" s="2"/>
@@ -68163,7 +68171,7 @@
         <v>75</v>
       </c>
       <c r="AG566" t="s" s="2">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="AH566" t="s" s="2">
         <v>76</v>
@@ -68180,13 +68188,13 @@
     </row>
     <row r="567">
       <c r="A567" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="D567" s="2"/>
       <c r="E567" t="s" s="2">
@@ -68212,10 +68220,10 @@
         <v>448</v>
       </c>
       <c r="M567" t="s" s="2">
+        <v>1498</v>
+      </c>
+      <c r="N567" t="s" s="2">
         <v>1499</v>
-      </c>
-      <c r="N567" t="s" s="2">
-        <v>1500</v>
       </c>
       <c r="O567" s="2"/>
       <c r="P567" s="2"/>
@@ -68266,7 +68274,7 @@
         <v>75</v>
       </c>
       <c r="AG567" t="s" s="2">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="AH567" t="s" s="2">
         <v>76</v>
@@ -68283,13 +68291,13 @@
     </row>
     <row r="568">
       <c r="A568" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B568" t="s" s="2">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="C568" t="s" s="2">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D568" s="2"/>
       <c r="E568" t="s" s="2">
@@ -68312,13 +68320,13 @@
         <v>75</v>
       </c>
       <c r="L568" t="s" s="2">
+        <v>1501</v>
+      </c>
+      <c r="M568" t="s" s="2">
         <v>1502</v>
       </c>
-      <c r="M568" t="s" s="2">
+      <c r="N568" t="s" s="2">
         <v>1503</v>
-      </c>
-      <c r="N568" t="s" s="2">
-        <v>1504</v>
       </c>
       <c r="O568" s="2"/>
       <c r="P568" s="2"/>
@@ -68369,7 +68377,7 @@
         <v>75</v>
       </c>
       <c r="AG568" t="s" s="2">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="AH568" t="s" s="2">
         <v>76</v>
@@ -68386,13 +68394,13 @@
     </row>
     <row r="569">
       <c r="A569" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="C569" t="s" s="2">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D569" s="2"/>
       <c r="E569" t="s" s="2">
@@ -68418,10 +68426,10 @@
         <v>229</v>
       </c>
       <c r="M569" t="s" s="2">
+        <v>1505</v>
+      </c>
+      <c r="N569" t="s" s="2">
         <v>1506</v>
-      </c>
-      <c r="N569" t="s" s="2">
-        <v>1507</v>
       </c>
       <c r="O569" s="2"/>
       <c r="P569" s="2"/>
@@ -68472,7 +68480,7 @@
         <v>75</v>
       </c>
       <c r="AG569" t="s" s="2">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="AH569" t="s" s="2">
         <v>76</v>
@@ -68489,13 +68497,13 @@
     </row>
     <row r="570">
       <c r="A570" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="C570" t="s" s="2">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D570" s="2"/>
       <c r="E570" t="s" s="2">
@@ -68518,13 +68526,13 @@
         <v>75</v>
       </c>
       <c r="L570" t="s" s="2">
+        <v>1508</v>
+      </c>
+      <c r="M570" t="s" s="2">
+        <v>1505</v>
+      </c>
+      <c r="N570" t="s" s="2">
         <v>1509</v>
-      </c>
-      <c r="M570" t="s" s="2">
-        <v>1506</v>
-      </c>
-      <c r="N570" t="s" s="2">
-        <v>1510</v>
       </c>
       <c r="O570" s="2"/>
       <c r="P570" s="2"/>
@@ -68575,7 +68583,7 @@
         <v>75</v>
       </c>
       <c r="AG570" t="s" s="2">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="AH570" t="s" s="2">
         <v>76</v>
@@ -68592,13 +68600,13 @@
     </row>
     <row r="571">
       <c r="A571" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B571" t="s" s="2">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C571" t="s" s="2">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="D571" s="2"/>
       <c r="E571" t="s" s="2">
@@ -68624,10 +68632,10 @@
         <v>506</v>
       </c>
       <c r="M571" t="s" s="2">
+        <v>1511</v>
+      </c>
+      <c r="N571" t="s" s="2">
         <v>1512</v>
-      </c>
-      <c r="N571" t="s" s="2">
-        <v>1513</v>
       </c>
       <c r="O571" s="2"/>
       <c r="P571" s="2"/>
@@ -68678,7 +68686,7 @@
         <v>75</v>
       </c>
       <c r="AG571" t="s" s="2">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="AH571" t="s" s="2">
         <v>76</v>
@@ -68695,13 +68703,13 @@
     </row>
     <row r="572">
       <c r="A572" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C572" t="s" s="2">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="D572" s="2"/>
       <c r="E572" t="s" s="2">
@@ -68727,10 +68735,10 @@
         <v>772</v>
       </c>
       <c r="M572" t="s" s="2">
+        <v>1514</v>
+      </c>
+      <c r="N572" t="s" s="2">
         <v>1515</v>
-      </c>
-      <c r="N572" t="s" s="2">
-        <v>1516</v>
       </c>
       <c r="O572" s="2"/>
       <c r="P572" s="2"/>
@@ -68781,7 +68789,7 @@
         <v>75</v>
       </c>
       <c r="AG572" t="s" s="2">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="AH572" t="s" s="2">
         <v>76</v>
@@ -68793,18 +68801,18 @@
         <v>75</v>
       </c>
       <c r="AK572" t="s" s="2">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C573" t="s" s="2">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="D573" s="2"/>
       <c r="E573" t="s" s="2">
@@ -68901,13 +68909,13 @@
     </row>
     <row r="574">
       <c r="A574" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B574" t="s" s="2">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C574" t="s" s="2">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="D574" s="2"/>
       <c r="E574" t="s" s="2">
@@ -69006,13 +69014,13 @@
     </row>
     <row r="575">
       <c r="A575" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B575" t="s" s="2">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C575" t="s" s="2">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="D575" s="2"/>
       <c r="E575" t="s" s="2">
@@ -69113,13 +69121,13 @@
     </row>
     <row r="576">
       <c r="A576" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B576" t="s" s="2">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="C576" t="s" s="2">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="D576" s="2"/>
       <c r="E576" t="s" s="2">
@@ -69145,10 +69153,10 @@
         <v>86</v>
       </c>
       <c r="M576" t="s" s="2">
+        <v>1521</v>
+      </c>
+      <c r="N576" t="s" s="2">
         <v>1522</v>
-      </c>
-      <c r="N576" t="s" s="2">
-        <v>1523</v>
       </c>
       <c r="O576" s="2"/>
       <c r="P576" s="2"/>
@@ -69199,7 +69207,7 @@
         <v>75</v>
       </c>
       <c r="AG576" t="s" s="2">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="AH576" t="s" s="2">
         <v>76</v>
@@ -69216,13 +69224,13 @@
     </row>
     <row r="577">
       <c r="A577" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B577" t="s" s="2">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="C577" t="s" s="2">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="D577" s="2"/>
       <c r="E577" t="s" s="2">
@@ -69248,10 +69256,10 @@
         <v>86</v>
       </c>
       <c r="M577" t="s" s="2">
+        <v>1524</v>
+      </c>
+      <c r="N577" t="s" s="2">
         <v>1525</v>
-      </c>
-      <c r="N577" t="s" s="2">
-        <v>1526</v>
       </c>
       <c r="O577" s="2"/>
       <c r="P577" s="2"/>
@@ -69302,7 +69310,7 @@
         <v>75</v>
       </c>
       <c r="AG577" t="s" s="2">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="AH577" t="s" s="2">
         <v>76</v>
@@ -69319,13 +69327,13 @@
     </row>
     <row r="578">
       <c r="A578" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B578" t="s" s="2">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C578" t="s" s="2">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="D578" s="2"/>
       <c r="E578" t="s" s="2">
@@ -69351,10 +69359,10 @@
         <v>86</v>
       </c>
       <c r="M578" t="s" s="2">
+        <v>1527</v>
+      </c>
+      <c r="N578" t="s" s="2">
         <v>1528</v>
-      </c>
-      <c r="N578" t="s" s="2">
-        <v>1529</v>
       </c>
       <c r="O578" s="2"/>
       <c r="P578" s="2"/>
@@ -69405,7 +69413,7 @@
         <v>75</v>
       </c>
       <c r="AG578" t="s" s="2">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="AH578" t="s" s="2">
         <v>76</v>
@@ -69422,13 +69430,13 @@
     </row>
     <row r="579">
       <c r="A579" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B579" t="s" s="2">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C579" t="s" s="2">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="D579" s="2"/>
       <c r="E579" t="s" s="2">
@@ -69454,10 +69462,10 @@
         <v>86</v>
       </c>
       <c r="M579" t="s" s="2">
+        <v>1530</v>
+      </c>
+      <c r="N579" t="s" s="2">
         <v>1531</v>
-      </c>
-      <c r="N579" t="s" s="2">
-        <v>1532</v>
       </c>
       <c r="O579" s="2"/>
       <c r="P579" s="2"/>
@@ -69508,7 +69516,7 @@
         <v>75</v>
       </c>
       <c r="AG579" t="s" s="2">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="AH579" t="s" s="2">
         <v>76</v>
@@ -69525,13 +69533,13 @@
     </row>
     <row r="580">
       <c r="A580" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B580" t="s" s="2">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="C580" t="s" s="2">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="D580" s="2"/>
       <c r="E580" t="s" s="2">
@@ -69560,7 +69568,7 @@
         <v>375</v>
       </c>
       <c r="N580" t="s" s="2">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="O580" s="2"/>
       <c r="P580" s="2"/>
@@ -69611,7 +69619,7 @@
         <v>75</v>
       </c>
       <c r="AG580" t="s" s="2">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="AH580" t="s" s="2">
         <v>76</v>
@@ -69628,13 +69636,13 @@
     </row>
     <row r="581">
       <c r="A581" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B581" t="s" s="2">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="C581" t="s" s="2">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="D581" s="2"/>
       <c r="E581" t="s" s="2">
@@ -69660,10 +69668,10 @@
         <v>229</v>
       </c>
       <c r="M581" t="s" s="2">
+        <v>1535</v>
+      </c>
+      <c r="N581" t="s" s="2">
         <v>1536</v>
-      </c>
-      <c r="N581" t="s" s="2">
-        <v>1537</v>
       </c>
       <c r="O581" s="2"/>
       <c r="P581" s="2"/>
@@ -69714,7 +69722,7 @@
         <v>75</v>
       </c>
       <c r="AG581" t="s" s="2">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="AH581" t="s" s="2">
         <v>76</v>
@@ -69731,13 +69739,13 @@
     </row>
     <row r="582">
       <c r="A582" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B582" t="s" s="2">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="C582" t="s" s="2">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="D582" s="2"/>
       <c r="E582" t="s" s="2">
@@ -69760,13 +69768,13 @@
         <v>75</v>
       </c>
       <c r="L582" t="s" s="2">
+        <v>1538</v>
+      </c>
+      <c r="M582" t="s" s="2">
         <v>1539</v>
       </c>
-      <c r="M582" t="s" s="2">
+      <c r="N582" t="s" s="2">
         <v>1540</v>
-      </c>
-      <c r="N582" t="s" s="2">
-        <v>1541</v>
       </c>
       <c r="O582" s="2"/>
       <c r="P582" s="2"/>
@@ -69817,7 +69825,7 @@
         <v>75</v>
       </c>
       <c r="AG582" t="s" s="2">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="AH582" t="s" s="2">
         <v>76</v>
@@ -69834,13 +69842,13 @@
     </row>
     <row r="583">
       <c r="A583" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B583" t="s" s="2">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="C583" t="s" s="2">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="D583" s="2"/>
       <c r="E583" t="s" s="2">
@@ -69866,13 +69874,13 @@
         <v>772</v>
       </c>
       <c r="M583" t="s" s="2">
+        <v>1542</v>
+      </c>
+      <c r="N583" t="s" s="2">
         <v>1543</v>
       </c>
-      <c r="N583" t="s" s="2">
+      <c r="O583" t="s" s="2">
         <v>1544</v>
-      </c>
-      <c r="O583" t="s" s="2">
-        <v>1545</v>
       </c>
       <c r="P583" s="2"/>
       <c r="Q583" t="s" s="2">
@@ -69922,7 +69930,7 @@
         <v>75</v>
       </c>
       <c r="AG583" t="s" s="2">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="AH583" t="s" s="2">
         <v>76</v>
@@ -69939,13 +69947,13 @@
     </row>
     <row r="584">
       <c r="A584" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B584" t="s" s="2">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="C584" t="s" s="2">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D584" s="2"/>
       <c r="E584" t="s" s="2">
@@ -70042,13 +70050,13 @@
     </row>
     <row r="585">
       <c r="A585" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B585" t="s" s="2">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="C585" t="s" s="2">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="D585" s="2"/>
       <c r="E585" t="s" s="2">
@@ -70147,13 +70155,13 @@
     </row>
     <row r="586">
       <c r="A586" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B586" t="s" s="2">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="C586" t="s" s="2">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="D586" s="2"/>
       <c r="E586" t="s" s="2">
@@ -70254,13 +70262,13 @@
     </row>
     <row r="587">
       <c r="A587" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B587" t="s" s="2">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="C587" t="s" s="2">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="D587" s="2"/>
       <c r="E587" t="s" s="2">
@@ -70286,13 +70294,13 @@
         <v>149</v>
       </c>
       <c r="M587" t="s" s="2">
+        <v>1549</v>
+      </c>
+      <c r="N587" t="s" s="2">
         <v>1550</v>
       </c>
-      <c r="N587" t="s" s="2">
+      <c r="O587" t="s" s="2">
         <v>1551</v>
-      </c>
-      <c r="O587" t="s" s="2">
-        <v>1552</v>
       </c>
       <c r="P587" s="2"/>
       <c r="Q587" t="s" s="2">
@@ -70321,11 +70329,11 @@
         <v>154</v>
       </c>
       <c r="Z587" t="s" s="2">
+        <v>1552</v>
+      </c>
+      <c r="AA587" t="s" s="2">
         <v>1553</v>
       </c>
-      <c r="AA587" t="s" s="2">
-        <v>1554</v>
-      </c>
       <c r="AB587" t="s" s="2">
         <v>75</v>
       </c>
@@ -70342,7 +70350,7 @@
         <v>75</v>
       </c>
       <c r="AG587" t="s" s="2">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="AH587" t="s" s="2">
         <v>85</v>
@@ -70359,13 +70367,13 @@
     </row>
     <row r="588">
       <c r="A588" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B588" t="s" s="2">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="C588" t="s" s="2">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="D588" s="2"/>
       <c r="E588" t="s" s="2">
@@ -70388,16 +70396,16 @@
         <v>75</v>
       </c>
       <c r="L588" t="s" s="2">
+        <v>1555</v>
+      </c>
+      <c r="M588" t="s" s="2">
         <v>1556</v>
       </c>
-      <c r="M588" t="s" s="2">
+      <c r="N588" t="s" s="2">
         <v>1557</v>
       </c>
-      <c r="N588" t="s" s="2">
+      <c r="O588" t="s" s="2">
         <v>1558</v>
-      </c>
-      <c r="O588" t="s" s="2">
-        <v>1559</v>
       </c>
       <c r="P588" s="2"/>
       <c r="Q588" t="s" s="2">
@@ -70447,7 +70455,7 @@
         <v>75</v>
       </c>
       <c r="AG588" t="s" s="2">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="AH588" t="s" s="2">
         <v>76</v>
@@ -70464,13 +70472,13 @@
     </row>
     <row r="589">
       <c r="A589" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B589" t="s" s="2">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="C589" t="s" s="2">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D589" s="2"/>
       <c r="E589" t="s" s="2">
@@ -70496,10 +70504,10 @@
         <v>772</v>
       </c>
       <c r="M589" t="s" s="2">
+        <v>1560</v>
+      </c>
+      <c r="N589" t="s" s="2">
         <v>1561</v>
-      </c>
-      <c r="N589" t="s" s="2">
-        <v>1562</v>
       </c>
       <c r="O589" s="2"/>
       <c r="P589" s="2"/>
@@ -70550,7 +70558,7 @@
         <v>75</v>
       </c>
       <c r="AG589" t="s" s="2">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="AH589" t="s" s="2">
         <v>76</v>
@@ -70567,13 +70575,13 @@
     </row>
     <row r="590">
       <c r="A590" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B590" t="s" s="2">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="C590" t="s" s="2">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="D590" s="2"/>
       <c r="E590" t="s" s="2">
@@ -70670,13 +70678,13 @@
     </row>
     <row r="591">
       <c r="A591" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B591" t="s" s="2">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="C591" t="s" s="2">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="D591" s="2"/>
       <c r="E591" t="s" s="2">
@@ -70771,16 +70779,16 @@
     </row>
     <row r="592">
       <c r="A592" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B592" t="s" s="2">
+        <v>1564</v>
+      </c>
+      <c r="C592" t="s" s="2">
+        <v>1563</v>
+      </c>
+      <c r="D592" t="s" s="2">
         <v>1565</v>
-      </c>
-      <c r="C592" t="s" s="2">
-        <v>1564</v>
-      </c>
-      <c r="D592" t="s" s="2">
-        <v>1566</v>
       </c>
       <c r="E592" t="s" s="2">
         <v>75</v>
@@ -70802,13 +70810,13 @@
         <v>75</v>
       </c>
       <c r="L592" t="s" s="2">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M592" t="s" s="2">
         <v>175</v>
       </c>
       <c r="N592" t="s" s="2">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="O592" s="2"/>
       <c r="P592" s="2"/>
@@ -70876,13 +70884,13 @@
     </row>
     <row r="593">
       <c r="A593" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B593" t="s" s="2">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="C593" t="s" s="2">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="D593" s="2"/>
       <c r="E593" t="s" s="2">
@@ -70983,13 +70991,13 @@
     </row>
     <row r="594">
       <c r="A594" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B594" t="s" s="2">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="C594" t="s" s="2">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="D594" s="2"/>
       <c r="E594" t="s" s="2">
@@ -71015,10 +71023,10 @@
         <v>257</v>
       </c>
       <c r="M594" t="s" s="2">
+        <v>1570</v>
+      </c>
+      <c r="N594" t="s" s="2">
         <v>1571</v>
-      </c>
-      <c r="N594" t="s" s="2">
-        <v>1572</v>
       </c>
       <c r="O594" s="2"/>
       <c r="P594" s="2"/>
@@ -71069,7 +71077,7 @@
         <v>75</v>
       </c>
       <c r="AG594" t="s" s="2">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="AH594" t="s" s="2">
         <v>85</v>
@@ -71086,13 +71094,13 @@
     </row>
     <row r="595">
       <c r="A595" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B595" t="s" s="2">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="C595" t="s" s="2">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="D595" s="2"/>
       <c r="E595" t="s" s="2">
@@ -71118,10 +71126,10 @@
         <v>149</v>
       </c>
       <c r="M595" t="s" s="2">
+        <v>1573</v>
+      </c>
+      <c r="N595" t="s" s="2">
         <v>1574</v>
-      </c>
-      <c r="N595" t="s" s="2">
-        <v>1575</v>
       </c>
       <c r="O595" s="2"/>
       <c r="P595" s="2"/>
@@ -71151,11 +71159,11 @@
         <v>154</v>
       </c>
       <c r="Z595" t="s" s="2">
+        <v>1575</v>
+      </c>
+      <c r="AA595" t="s" s="2">
         <v>1576</v>
       </c>
-      <c r="AA595" t="s" s="2">
-        <v>1577</v>
-      </c>
       <c r="AB595" t="s" s="2">
         <v>75</v>
       </c>
@@ -71172,7 +71180,7 @@
         <v>75</v>
       </c>
       <c r="AG595" t="s" s="2">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="AH595" t="s" s="2">
         <v>85</v>
@@ -71189,13 +71197,13 @@
     </row>
     <row r="596">
       <c r="A596" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B596" t="s" s="2">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="C596" t="s" s="2">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="D596" s="2"/>
       <c r="E596" t="s" s="2">
@@ -71218,13 +71226,13 @@
         <v>75</v>
       </c>
       <c r="L596" t="s" s="2">
+        <v>1578</v>
+      </c>
+      <c r="M596" t="s" s="2">
         <v>1579</v>
       </c>
-      <c r="M596" t="s" s="2">
+      <c r="N596" t="s" s="2">
         <v>1580</v>
-      </c>
-      <c r="N596" t="s" s="2">
-        <v>1581</v>
       </c>
       <c r="O596" s="2"/>
       <c r="P596" s="2"/>
@@ -71275,7 +71283,7 @@
         <v>75</v>
       </c>
       <c r="AG596" t="s" s="2">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="AH596" t="s" s="2">
         <v>76</v>
@@ -71292,13 +71300,13 @@
     </row>
     <row r="597">
       <c r="A597" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B597" t="s" s="2">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="C597" t="s" s="2">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="D597" s="2"/>
       <c r="E597" t="s" s="2">
@@ -71321,13 +71329,13 @@
         <v>75</v>
       </c>
       <c r="L597" t="s" s="2">
+        <v>1582</v>
+      </c>
+      <c r="M597" t="s" s="2">
         <v>1583</v>
       </c>
-      <c r="M597" t="s" s="2">
+      <c r="N597" t="s" s="2">
         <v>1584</v>
-      </c>
-      <c r="N597" t="s" s="2">
-        <v>1585</v>
       </c>
       <c r="O597" s="2"/>
       <c r="P597" s="2"/>
@@ -71378,7 +71386,7 @@
         <v>75</v>
       </c>
       <c r="AG597" t="s" s="2">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="AH597" t="s" s="2">
         <v>76</v>
@@ -71395,13 +71403,13 @@
     </row>
     <row r="598">
       <c r="A598" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B598" t="s" s="2">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="C598" t="s" s="2">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="D598" s="2"/>
       <c r="E598" t="s" s="2">
@@ -71424,13 +71432,13 @@
         <v>75</v>
       </c>
       <c r="L598" t="s" s="2">
+        <v>1586</v>
+      </c>
+      <c r="M598" t="s" s="2">
         <v>1587</v>
       </c>
-      <c r="M598" t="s" s="2">
+      <c r="N598" t="s" s="2">
         <v>1588</v>
-      </c>
-      <c r="N598" t="s" s="2">
-        <v>1589</v>
       </c>
       <c r="O598" s="2"/>
       <c r="P598" s="2"/>
@@ -71481,7 +71489,7 @@
         <v>75</v>
       </c>
       <c r="AG598" t="s" s="2">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="AH598" t="s" s="2">
         <v>76</v>
@@ -71498,13 +71506,13 @@
     </row>
     <row r="599">
       <c r="A599" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B599" t="s" s="2">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="C599" t="s" s="2">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="D599" s="2"/>
       <c r="E599" t="s" s="2">
@@ -71530,10 +71538,10 @@
         <v>229</v>
       </c>
       <c r="M599" t="s" s="2">
+        <v>1590</v>
+      </c>
+      <c r="N599" t="s" s="2">
         <v>1591</v>
-      </c>
-      <c r="N599" t="s" s="2">
-        <v>1592</v>
       </c>
       <c r="O599" s="2"/>
       <c r="P599" s="2"/>
@@ -71563,11 +71571,11 @@
         <v>318</v>
       </c>
       <c r="Z599" t="s" s="2">
+        <v>1592</v>
+      </c>
+      <c r="AA599" t="s" s="2">
         <v>1593</v>
       </c>
-      <c r="AA599" t="s" s="2">
-        <v>1594</v>
-      </c>
       <c r="AB599" t="s" s="2">
         <v>75</v>
       </c>
@@ -71584,7 +71592,7 @@
         <v>75</v>
       </c>
       <c r="AG599" t="s" s="2">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="AH599" t="s" s="2">
         <v>76</v>
@@ -71601,13 +71609,13 @@
     </row>
     <row r="600">
       <c r="A600" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B600" t="s" s="2">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="C600" t="s" s="2">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="D600" s="2"/>
       <c r="E600" t="s" s="2">
@@ -71633,10 +71641,10 @@
         <v>149</v>
       </c>
       <c r="M600" t="s" s="2">
+        <v>1595</v>
+      </c>
+      <c r="N600" t="s" s="2">
         <v>1596</v>
-      </c>
-      <c r="N600" t="s" s="2">
-        <v>1597</v>
       </c>
       <c r="O600" s="2"/>
       <c r="P600" s="2"/>
@@ -71666,11 +71674,11 @@
         <v>154</v>
       </c>
       <c r="Z600" t="s" s="2">
+        <v>1597</v>
+      </c>
+      <c r="AA600" t="s" s="2">
         <v>1598</v>
       </c>
-      <c r="AA600" t="s" s="2">
-        <v>1599</v>
-      </c>
       <c r="AB600" t="s" s="2">
         <v>75</v>
       </c>
@@ -71687,7 +71695,7 @@
         <v>75</v>
       </c>
       <c r="AG600" t="s" s="2">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="AH600" t="s" s="2">
         <v>76</v>
@@ -71704,13 +71712,13 @@
     </row>
     <row r="601">
       <c r="A601" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B601" t="s" s="2">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="C601" t="s" s="2">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="D601" s="2"/>
       <c r="E601" t="s" s="2">
@@ -71736,10 +71744,10 @@
         <v>149</v>
       </c>
       <c r="M601" t="s" s="2">
+        <v>1600</v>
+      </c>
+      <c r="N601" t="s" s="2">
         <v>1601</v>
-      </c>
-      <c r="N601" t="s" s="2">
-        <v>1602</v>
       </c>
       <c r="O601" s="2"/>
       <c r="P601" s="2"/>
@@ -71769,11 +71777,11 @@
         <v>154</v>
       </c>
       <c r="Z601" t="s" s="2">
+        <v>1602</v>
+      </c>
+      <c r="AA601" t="s" s="2">
         <v>1603</v>
       </c>
-      <c r="AA601" t="s" s="2">
-        <v>1604</v>
-      </c>
       <c r="AB601" t="s" s="2">
         <v>75</v>
       </c>
@@ -71790,7 +71798,7 @@
         <v>75</v>
       </c>
       <c r="AG601" t="s" s="2">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="AH601" t="s" s="2">
         <v>76</v>
@@ -71807,13 +71815,13 @@
     </row>
     <row r="602">
       <c r="A602" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B602" t="s" s="2">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="C602" t="s" s="2">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="D602" s="2"/>
       <c r="E602" t="s" s="2">
@@ -71839,10 +71847,10 @@
         <v>149</v>
       </c>
       <c r="M602" t="s" s="2">
+        <v>1605</v>
+      </c>
+      <c r="N602" t="s" s="2">
         <v>1606</v>
-      </c>
-      <c r="N602" t="s" s="2">
-        <v>1607</v>
       </c>
       <c r="O602" s="2"/>
       <c r="P602" s="2"/>
@@ -71872,11 +71880,11 @@
         <v>154</v>
       </c>
       <c r="Z602" t="s" s="2">
+        <v>1607</v>
+      </c>
+      <c r="AA602" t="s" s="2">
         <v>1608</v>
       </c>
-      <c r="AA602" t="s" s="2">
-        <v>1609</v>
-      </c>
       <c r="AB602" t="s" s="2">
         <v>75</v>
       </c>
@@ -71893,7 +71901,7 @@
         <v>75</v>
       </c>
       <c r="AG602" t="s" s="2">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="AH602" t="s" s="2">
         <v>76</v>
@@ -71910,13 +71918,13 @@
     </row>
     <row r="603">
       <c r="A603" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B603" t="s" s="2">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="C603" t="s" s="2">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="D603" s="2"/>
       <c r="E603" t="s" s="2">
@@ -71942,10 +71950,10 @@
         <v>149</v>
       </c>
       <c r="M603" t="s" s="2">
+        <v>1610</v>
+      </c>
+      <c r="N603" t="s" s="2">
         <v>1611</v>
-      </c>
-      <c r="N603" t="s" s="2">
-        <v>1612</v>
       </c>
       <c r="O603" s="2"/>
       <c r="P603" s="2"/>
@@ -71975,11 +71983,11 @@
         <v>154</v>
       </c>
       <c r="Z603" t="s" s="2">
+        <v>1612</v>
+      </c>
+      <c r="AA603" t="s" s="2">
         <v>1613</v>
       </c>
-      <c r="AA603" t="s" s="2">
-        <v>1614</v>
-      </c>
       <c r="AB603" t="s" s="2">
         <v>75</v>
       </c>
@@ -71996,7 +72004,7 @@
         <v>75</v>
       </c>
       <c r="AG603" t="s" s="2">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AH603" t="s" s="2">
         <v>76</v>
@@ -72013,13 +72021,13 @@
     </row>
     <row r="604">
       <c r="A604" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B604" t="s" s="2">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="C604" t="s" s="2">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="D604" s="2"/>
       <c r="E604" t="s" s="2">
@@ -72045,10 +72053,10 @@
         <v>149</v>
       </c>
       <c r="M604" t="s" s="2">
+        <v>1615</v>
+      </c>
+      <c r="N604" t="s" s="2">
         <v>1616</v>
-      </c>
-      <c r="N604" t="s" s="2">
-        <v>1617</v>
       </c>
       <c r="O604" s="2"/>
       <c r="P604" s="2"/>
@@ -72078,11 +72086,11 @@
         <v>154</v>
       </c>
       <c r="Z604" t="s" s="2">
+        <v>1617</v>
+      </c>
+      <c r="AA604" t="s" s="2">
         <v>1618</v>
       </c>
-      <c r="AA604" t="s" s="2">
-        <v>1619</v>
-      </c>
       <c r="AB604" t="s" s="2">
         <v>75</v>
       </c>
@@ -72099,7 +72107,7 @@
         <v>75</v>
       </c>
       <c r="AG604" t="s" s="2">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="AH604" t="s" s="2">
         <v>76</v>
@@ -72116,13 +72124,13 @@
     </row>
     <row r="605">
       <c r="A605" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B605" t="s" s="2">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="C605" t="s" s="2">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="D605" s="2"/>
       <c r="E605" t="s" s="2">
@@ -72148,13 +72156,13 @@
         <v>414</v>
       </c>
       <c r="M605" t="s" s="2">
+        <v>1620</v>
+      </c>
+      <c r="N605" t="s" s="2">
         <v>1621</v>
       </c>
-      <c r="N605" t="s" s="2">
+      <c r="O605" t="s" s="2">
         <v>1622</v>
-      </c>
-      <c r="O605" t="s" s="2">
-        <v>1623</v>
       </c>
       <c r="P605" s="2"/>
       <c r="Q605" t="s" s="2">
@@ -72204,7 +72212,7 @@
         <v>75</v>
       </c>
       <c r="AG605" t="s" s="2">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="AH605" t="s" s="2">
         <v>76</v>
@@ -72213,7 +72221,7 @@
         <v>85</v>
       </c>
       <c r="AJ605" t="s" s="2">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="AK605" t="s" s="2">
         <v>107</v>
@@ -72221,13 +72229,13 @@
     </row>
     <row r="606">
       <c r="A606" t="s" s="2">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B606" t="s" s="2">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="C606" t="s" s="2">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="D606" s="2"/>
       <c r="E606" t="s" s="2">
@@ -72253,10 +72261,10 @@
         <v>78</v>
       </c>
       <c r="M606" t="s" s="2">
+        <v>1625</v>
+      </c>
+      <c r="N606" t="s" s="2">
         <v>1626</v>
-      </c>
-      <c r="N606" t="s" s="2">
-        <v>1627</v>
       </c>
       <c r="O606" s="2"/>
       <c r="P606" s="2"/>
@@ -72307,7 +72315,7 @@
         <v>75</v>
       </c>
       <c r="AG606" t="s" s="2">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="AH606" t="s" s="2">
         <v>76</v>
@@ -72316,7 +72324,7 @@
         <v>77</v>
       </c>
       <c r="AJ606" t="s" s="2">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="AK606" t="s" s="2">
         <v>107</v>
@@ -72324,7 +72332,7 @@
     </row>
     <row r="607">
       <c r="A607" t="s" s="2">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B607" t="s" s="2">
         <v>177</v>
@@ -72356,10 +72364,10 @@
         <v>78</v>
       </c>
       <c r="M607" t="s" s="2">
+        <v>1629</v>
+      </c>
+      <c r="N607" t="s" s="2">
         <v>1630</v>
-      </c>
-      <c r="N607" t="s" s="2">
-        <v>1631</v>
       </c>
       <c r="O607" s="2"/>
       <c r="P607" s="2"/>
@@ -72427,7 +72435,7 @@
     </row>
     <row r="608">
       <c r="A608" t="s" s="2">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B608" t="s" s="2">
         <v>182</v>
@@ -72530,7 +72538,7 @@
     </row>
     <row r="609">
       <c r="A609" t="s" s="2">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B609" t="s" s="2">
         <v>183</v>
@@ -72633,7 +72641,7 @@
     </row>
     <row r="610">
       <c r="A610" t="s" s="2">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B610" t="s" s="2">
         <v>185</v>
@@ -72738,7 +72746,7 @@
     </row>
     <row r="611">
       <c r="A611" t="s" s="2">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B611" t="s" s="2">
         <v>189</v>
@@ -72843,7 +72851,7 @@
     </row>
     <row r="612">
       <c r="A612" t="s" s="2">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B612" t="s" s="2">
         <v>177</v>
@@ -72946,7 +72954,7 @@
     </row>
     <row r="613">
       <c r="A613" t="s" s="2">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B613" t="s" s="2">
         <v>182</v>
@@ -73049,7 +73057,7 @@
     </row>
     <row r="614">
       <c r="A614" t="s" s="2">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B614" t="s" s="2">
         <v>183</v>
@@ -73152,7 +73160,7 @@
     </row>
     <row r="615">
       <c r="A615" t="s" s="2">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B615" t="s" s="2">
         <v>185</v>
@@ -73198,7 +73206,7 @@
       </c>
       <c r="R615" s="2"/>
       <c r="S615" t="s" s="2">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="T615" t="s" s="2">
         <v>75</v>
@@ -73257,7 +73265,7 @@
     </row>
     <row r="616">
       <c r="A616" t="s" s="2">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B616" t="s" s="2">
         <v>189</v>
@@ -73323,7 +73331,7 @@
       </c>
       <c r="Z616" s="2"/>
       <c r="AA616" t="s" s="2">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="AB616" t="s" s="2">
         <v>75</v>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T12:57:50+00:00</t>
+    <t>2025-12-29T13:00:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:00:52+00:00</t>
+    <t>2025-12-29T13:00:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:00:32+00:00</t>
+    <t>2025-12-29T13:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:15:57+00:00</t>
+    <t>2025-12-29T13:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:18:38+00:00</t>
+    <t>2025-12-29T13:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:24:54+00:00</t>
+    <t>2025-12-29T13:29:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:29:27+00:00</t>
+    <t>2025-12-29T13:42:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T13:42:20+00:00</t>
+    <t>2025-12-29T14:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T14:29:02+00:00</t>
+    <t>2025-12-29T14:27:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T14:27:33+00:00</t>
+    <t>2025-12-29T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T14:28:10+00:00</t>
+    <t>2025-12-29T14:39:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T14:39:46+00:00</t>
+    <t>2025-12-29T15:02:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T15:02:13+00:00</t>
+    <t>2025-12-29T15:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T15:10:06+00:00</t>
+    <t>2025-12-29T15:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T15:27:17+00:00</t>
+    <t>2025-12-29T15:39:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T15:39:17+00:00</t>
+    <t>2025-12-29T15:51:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T15:51:46+00:00</t>
+    <t>2025-12-29T16:00:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T16:00:26+00:00</t>
+    <t>2025-12-29T16:05:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-29T16:05:48+00:00</t>
+    <t>2026-01-09T13:44:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-pages/ig/all-profiles.xlsx
+++ b/nr-update-pages/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-09T13:44:02+00:00</t>
+    <t>2026-01-16T18:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
